--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-05.xlsx
@@ -544,12 +544,12 @@
     <t>Psim Yogyakarta</t>
   </si>
   <si>
+    <t>Persik Kediri</t>
+  </si>
+  <si>
     <t>Bhayangkara FC</t>
   </si>
   <si>
-    <t>Persik Kediri</t>
-  </si>
-  <si>
     <t>Kryvbas Krivyi Rih</t>
   </si>
   <si>
@@ -988,12 +988,12 @@
     <t>Persita Tangerang</t>
   </si>
   <si>
+    <t>Dewa United FC</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
-    <t>Dewa United FC</t>
-  </si>
-  <si>
     <t>Kolos Kovalyovka</t>
   </si>
   <si>
@@ -1408,7 +1408,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-09-03 04:19:52</t>
+    <t>2026-09-03 06:35:31</t>
   </si>
 </sst>
 </file>
@@ -2005,7 +2005,7 @@
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
         <v>5.7</v>
@@ -2017,7 +2017,7 @@
         <v>4.1</v>
       </c>
       <c r="K2">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -2032,7 +2032,7 @@
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -2053,7 +2053,7 @@
         <v>1.11</v>
       </c>
       <c r="W2">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -2265,13 +2265,13 @@
         <v>1.33</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
         <v>1.84</v>
@@ -2280,130 +2280,130 @@
         <v>2.02</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
         <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2486,166 +2486,166 @@
         <v>318</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G4">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H4">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q4">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2728,7 +2728,7 @@
         <v>319</v>
       </c>
       <c r="F5">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>5.2</v>
@@ -2737,7 +2737,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="J5">
         <v>3.25</v>
@@ -2970,19 +2970,19 @@
         <v>320</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>2.1</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="K6">
         <v>250</v>
@@ -2994,22 +2994,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
         <v>1.16</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -3018,10 +3018,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -3212,22 +3212,22 @@
         <v>321</v>
       </c>
       <c r="F7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
         <v>4.5</v>
       </c>
       <c r="H7">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -3245,37 +3245,37 @@
         <v>1.94</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
         <v>1.29</v>
       </c>
       <c r="X7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB7">
         <v>16.5</v>
@@ -3302,7 +3302,7 @@
         <v>48</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK7">
         <v>65</v>
@@ -3317,19 +3317,19 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT7">
         <v>12</v>
@@ -3365,7 +3365,7 @@
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7">
         <v>32</v>
@@ -3472,208 +3472,208 @@
         <v>210</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
+        <v>1.35</v>
+      </c>
+      <c r="R8">
+        <v>1.15</v>
+      </c>
+      <c r="S8">
+        <v>1.02</v>
+      </c>
+      <c r="T8">
         <v>1.01</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>464</v>
@@ -3726,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3938,145 +3938,145 @@
         <v>324</v>
       </c>
       <c r="F10">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H10">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="I10">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="J10">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q10">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
@@ -4094,70 +4094,70 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
+        <v>21</v>
+      </c>
+      <c r="BG10">
+        <v>10.5</v>
+      </c>
+      <c r="BH10">
+        <v>3.95</v>
+      </c>
+      <c r="BI10">
+        <v>3.15</v>
+      </c>
+      <c r="BJ10">
+        <v>9</v>
+      </c>
+      <c r="BK10">
         <v>1.01</v>
       </c>
-      <c r="BG10">
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
         <v>1.01</v>
       </c>
-      <c r="BH10">
-        <v>0</v>
-      </c>
-      <c r="BI10">
-        <v>0</v>
-      </c>
-      <c r="BJ10">
-        <v>0</v>
-      </c>
-      <c r="BK10">
-        <v>0</v>
-      </c>
-      <c r="BL10">
-        <v>0</v>
-      </c>
-      <c r="BM10">
-        <v>0</v>
-      </c>
       <c r="BN10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>464</v>
@@ -4180,46 +4180,46 @@
         <v>325</v>
       </c>
       <c r="F11">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="H11">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="I11">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>1.37</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>200</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P11">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Q11">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -4228,97 +4228,97 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
         <v>1.01</v>
@@ -4336,70 +4336,70 @@
         <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>464</v>
@@ -4664,10 +4664,10 @@
         <v>327</v>
       </c>
       <c r="F13">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H13">
         <v>2.04</v>
@@ -4676,10 +4676,10 @@
         <v>2.28</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>210</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4906,28 +4906,28 @@
         <v>328</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="G14">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="H14">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="I14">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4936,10 +4936,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5390,22 +5390,22 @@
         <v>330</v>
       </c>
       <c r="F16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G16">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H16">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="K16">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -5632,22 +5632,22 @@
         <v>331</v>
       </c>
       <c r="F17">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G17">
         <v>2.44</v>
       </c>
       <c r="H17">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I17">
         <v>3.35</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -5662,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q17">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5883,13 +5883,13 @@
         <v>3.05</v>
       </c>
       <c r="I18">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J18">
         <v>3.7</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5904,10 +5904,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5916,10 +5916,10 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U18">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>55</v>
       </c>
       <c r="AB18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18">
         <v>9.199999999999999</v>
@@ -5949,7 +5949,7 @@
         <v>15</v>
       </c>
       <c r="AE18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF18">
         <v>19</v>
@@ -5967,22 +5967,22 @@
         <v>32</v>
       </c>
       <c r="AK18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM18">
         <v>60</v>
       </c>
       <c r="AN18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ18">
         <v>14.5</v>
@@ -5991,13 +5991,13 @@
         <v>21</v>
       </c>
       <c r="AS18">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
       </c>
       <c r="AU18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV18">
         <v>12</v>
@@ -6033,7 +6033,7 @@
         <v>11</v>
       </c>
       <c r="BG18">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BH18">
         <v>0</v>
@@ -6116,7 +6116,7 @@
         <v>333</v>
       </c>
       <c r="F19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G19">
         <v>1.35</v>
@@ -6125,7 +6125,7 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -6146,10 +6146,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -6158,10 +6158,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -6173,13 +6173,13 @@
         <v>36</v>
       </c>
       <c r="Y19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z19">
         <v>120</v>
       </c>
       <c r="AA19">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB19">
         <v>13</v>
@@ -6194,7 +6194,7 @@
         <v>150</v>
       </c>
       <c r="AF19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG19">
         <v>11.5</v>
@@ -6203,7 +6203,7 @@
         <v>25</v>
       </c>
       <c r="AI19">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ19">
         <v>12</v>
@@ -6212,7 +6212,7 @@
         <v>15.5</v>
       </c>
       <c r="AL19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM19">
         <v>120</v>
@@ -6221,7 +6221,7 @@
         <v>3.95</v>
       </c>
       <c r="AO19">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP19">
         <v>8.4</v>
@@ -6391,7 +6391,7 @@
         <v>1.96</v>
       </c>
       <c r="Q20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6600,13 +6600,13 @@
         <v>335</v>
       </c>
       <c r="F21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
         <v>2.84</v>
       </c>
       <c r="H21">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I21">
         <v>4.3</v>
@@ -6633,7 +6633,7 @@
         <v>1.75</v>
       </c>
       <c r="Q21">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6842,7 +6842,7 @@
         <v>336</v>
       </c>
       <c r="F22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G22">
         <v>2.28</v>
@@ -6869,19 +6869,19 @@
         <v>5.5</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.52</v>
       </c>
       <c r="Q22">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R22">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S22">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T22">
         <v>1.55</v>
@@ -6902,25 +6902,25 @@
         <v>18.5</v>
       </c>
       <c r="Z22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA22">
         <v>65</v>
       </c>
       <c r="AB22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC22">
         <v>9</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE22">
         <v>34</v>
       </c>
       <c r="AF22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG22">
         <v>11</v>
@@ -6935,16 +6935,16 @@
         <v>32</v>
       </c>
       <c r="AK22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL22">
         <v>27</v>
       </c>
       <c r="AM22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO22">
         <v>24</v>
@@ -6956,13 +6956,13 @@
         <v>16.5</v>
       </c>
       <c r="AR22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS22">
         <v>50</v>
       </c>
       <c r="AT22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU22">
         <v>8.6</v>
@@ -6974,7 +6974,7 @@
         <v>28</v>
       </c>
       <c r="AX22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY22">
         <v>10</v>
@@ -6989,13 +6989,13 @@
         <v>28</v>
       </c>
       <c r="BC22">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD22">
         <v>25</v>
       </c>
       <c r="BE22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF22">
         <v>11</v>
@@ -7084,22 +7084,22 @@
         <v>337</v>
       </c>
       <c r="F23">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H23">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>3.95</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -7329,16 +7329,16 @@
         <v>2.22</v>
       </c>
       <c r="G24">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I24">
         <v>3.45</v>
       </c>
       <c r="J24">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K24">
         <v>4.1</v>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q24">
         <v>1.72</v>
@@ -7568,22 +7568,22 @@
         <v>339</v>
       </c>
       <c r="F25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G25">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H25">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="I25">
         <v>2.12</v>
       </c>
       <c r="J25">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q25">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>1.61</v>
       </c>
       <c r="H26">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I26">
         <v>7.2</v>
@@ -7825,7 +7825,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7840,10 +7840,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q26">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -8052,7 +8052,7 @@
         <v>341</v>
       </c>
       <c r="F27">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
         <v>2.62</v>
@@ -8061,13 +8061,13 @@
         <v>2.88</v>
       </c>
       <c r="I27">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="J27">
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>2.26</v>
       </c>
       <c r="Q27">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
         <v>1.74</v>
@@ -8781,19 +8781,19 @@
         <v>2.2</v>
       </c>
       <c r="G30">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H30">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I30">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="J30">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K30">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8808,10 +8808,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -9023,7 +9023,7 @@
         <v>1.71</v>
       </c>
       <c r="G31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H31">
         <v>4.5</v>
@@ -9277,7 +9277,7 @@
         <v>3.85</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>2.38</v>
       </c>
       <c r="Q32">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>347</v>
       </c>
       <c r="F33">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G33">
         <v>2.84</v>
@@ -9537,7 +9537,7 @@
         <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9749,7 +9749,7 @@
         <v>2.32</v>
       </c>
       <c r="G34">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H34">
         <v>3.2</v>
@@ -9776,10 +9776,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -10747,7 +10747,7 @@
         <v>2.22</v>
       </c>
       <c r="Q38">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -11201,16 +11201,16 @@
         <v>2.72</v>
       </c>
       <c r="G40">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H40">
         <v>2.44</v>
       </c>
       <c r="I40">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="J40">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K40">
         <v>4.5</v>
@@ -11228,10 +11228,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11709,7 +11709,7 @@
         <v>3.4</v>
       </c>
       <c r="O42">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P42">
         <v>1.79</v>
@@ -11721,7 +11721,7 @@
         <v>1.3</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T42">
         <v>1.97</v>
@@ -11844,58 +11844,58 @@
         <v>36</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL42">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP42">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11954,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q43">
         <v>2.04</v>
@@ -12172,7 +12172,7 @@
         <v>4.5</v>
       </c>
       <c r="H44">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I44">
         <v>1.83</v>
@@ -12190,7 +12190,7 @@
         <v>1.03</v>
       </c>
       <c r="N44">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O44">
         <v>1.17</v>
@@ -12199,13 +12199,13 @@
         <v>2.84</v>
       </c>
       <c r="Q44">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S44">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T44">
         <v>1.54</v>
@@ -12226,7 +12226,7 @@
         <v>14.5</v>
       </c>
       <c r="Z44">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA44">
         <v>22</v>
@@ -12235,7 +12235,7 @@
         <v>25</v>
       </c>
       <c r="AC44">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD44">
         <v>10.5</v>
@@ -12250,7 +12250,7 @@
         <v>18</v>
       </c>
       <c r="AH44">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI44">
         <v>24</v>
@@ -12262,7 +12262,7 @@
         <v>44</v>
       </c>
       <c r="AL44">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM44">
         <v>55</v>
@@ -12277,7 +12277,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ44">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR44">
         <v>13</v>
@@ -12298,7 +12298,7 @@
         <v>14</v>
       </c>
       <c r="AX44">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AY44">
         <v>16</v>
@@ -12313,16 +12313,16 @@
         <v>36</v>
       </c>
       <c r="BC44">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BD44">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BE44">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF44">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BG44">
         <v>6.8</v>
@@ -12444,16 +12444,16 @@
         <v>1.69</v>
       </c>
       <c r="R45">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S45">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T45">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U45">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -12468,7 +12468,7 @@
         <v>12.5</v>
       </c>
       <c r="Z45">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA45">
         <v>27</v>
@@ -12504,7 +12504,7 @@
         <v>38</v>
       </c>
       <c r="AL45">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM45">
         <v>70</v>
@@ -12650,16 +12650,16 @@
         <v>360</v>
       </c>
       <c r="F46">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="H46">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I46">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J46">
         <v>5.2</v>
@@ -12671,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N46">
         <v>6.8</v>
@@ -12686,10 +12686,10 @@
         <v>1.46</v>
       </c>
       <c r="R46">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S46">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T46">
         <v>1.64</v>
@@ -12752,16 +12752,16 @@
         <v>75</v>
       </c>
       <c r="AN46">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO46">
         <v>65</v>
       </c>
       <c r="AP46">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AQ46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR46">
         <v>32</v>
@@ -12776,16 +12776,16 @@
         <v>11</v>
       </c>
       <c r="AV46">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW46">
         <v>34</v>
       </c>
       <c r="AX46">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY46">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ46">
         <v>16.5</v>
@@ -12794,7 +12794,7 @@
         <v>32</v>
       </c>
       <c r="BB46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC46">
         <v>11.5</v>
@@ -12812,55 +12812,55 @@
         <v>32</v>
       </c>
       <c r="BH46">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ46">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK46">
         <v>1.01</v>
       </c>
       <c r="BL46">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM46">
         <v>1.01</v>
       </c>
       <c r="BN46">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO46">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP46">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ46">
         <v>1.01</v>
       </c>
       <c r="BR46">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS46">
         <v>1.01</v>
       </c>
       <c r="BT46">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU46">
         <v>1.01</v>
       </c>
       <c r="BV46">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW46">
         <v>1.01</v>
       </c>
       <c r="BX46">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY46">
         <v>1.01</v>
@@ -12895,7 +12895,7 @@
         <v>3.1</v>
       </c>
       <c r="G47">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H47">
         <v>2.26</v>
@@ -12916,28 +12916,28 @@
         <v>1.03</v>
       </c>
       <c r="N47">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O47">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P47">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R47">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S47">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T47">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U47">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -12961,13 +12961,13 @@
         <v>22</v>
       </c>
       <c r="AC47">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD47">
         <v>12</v>
       </c>
       <c r="AE47">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF47">
         <v>29</v>
@@ -12976,16 +12976,16 @@
         <v>14.5</v>
       </c>
       <c r="AH47">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI47">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ47">
         <v>55</v>
       </c>
       <c r="AK47">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL47">
         <v>32</v>
@@ -12994,28 +12994,28 @@
         <v>46</v>
       </c>
       <c r="AN47">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO47">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP47">
         <v>21</v>
       </c>
       <c r="AQ47">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR47">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS47">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT47">
         <v>18.5</v>
       </c>
       <c r="AU47">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV47">
         <v>10.5</v>
@@ -13024,7 +13024,7 @@
         <v>16.5</v>
       </c>
       <c r="AX47">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AY47">
         <v>12.5</v>
@@ -13042,67 +13042,67 @@
         <v>18.5</v>
       </c>
       <c r="BD47">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE47">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BF47">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG47">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH47">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI47">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ47">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK47">
         <v>1.01</v>
       </c>
       <c r="BL47">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM47">
         <v>1.01</v>
       </c>
       <c r="BN47">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO47">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP47">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ47">
         <v>1.01</v>
       </c>
       <c r="BR47">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS47">
         <v>1.01</v>
       </c>
       <c r="BT47">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU47">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV47">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW47">
         <v>1.01</v>
       </c>
       <c r="BX47">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY47">
         <v>1.01</v>
@@ -13134,16 +13134,16 @@
         <v>362</v>
       </c>
       <c r="F48">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G48">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H48">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I48">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -13167,16 +13167,16 @@
         <v>2.48</v>
       </c>
       <c r="Q48">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R48">
         <v>1.6</v>
       </c>
       <c r="S48">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T48">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U48">
         <v>2.6</v>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="X48">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y48">
         <v>22</v>
@@ -13221,10 +13221,10 @@
         <v>15.5</v>
       </c>
       <c r="AI48">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ48">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK48">
         <v>18</v>
@@ -13233,19 +13233,19 @@
         <v>28</v>
       </c>
       <c r="AM48">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="AN48">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO48">
         <v>34</v>
       </c>
       <c r="AP48">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ48">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR48">
         <v>22</v>
@@ -13257,7 +13257,7 @@
         <v>11.5</v>
       </c>
       <c r="AU48">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV48">
         <v>15</v>
@@ -13266,10 +13266,10 @@
         <v>25</v>
       </c>
       <c r="AX48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY48">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ48">
         <v>13.5</v>
@@ -13278,7 +13278,7 @@
         <v>25</v>
       </c>
       <c r="BB48">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC48">
         <v>15</v>
@@ -13618,13 +13618,13 @@
         <v>364</v>
       </c>
       <c r="F50">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G50">
         <v>2.52</v>
       </c>
       <c r="H50">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <v>3.7</v>
@@ -13633,7 +13633,7 @@
         <v>3.6</v>
       </c>
       <c r="K50">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>4.2</v>
       </c>
       <c r="H51">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I51">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J51">
         <v>3.75</v>
       </c>
       <c r="K51">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13890,10 +13890,10 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q51">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -14132,7 +14132,7 @@
         <v>1.31</v>
       </c>
       <c r="P52">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q52">
         <v>1.93</v>
@@ -14141,13 +14141,13 @@
         <v>1.4</v>
       </c>
       <c r="S52">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T52">
         <v>1.79</v>
       </c>
       <c r="U52">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -14156,10 +14156,10 @@
         <v>0</v>
       </c>
       <c r="X52">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y52">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z52">
         <v>32</v>
@@ -14213,7 +14213,7 @@
         <v>14</v>
       </c>
       <c r="AQ52">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR52">
         <v>28</v>
@@ -14237,19 +14237,19 @@
         <v>11</v>
       </c>
       <c r="AY52">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ52">
         <v>16.5</v>
       </c>
       <c r="BA52">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB52">
         <v>20</v>
       </c>
       <c r="BC52">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD52">
         <v>30</v>
@@ -14592,7 +14592,7 @@
         <v>3.2</v>
       </c>
       <c r="H54">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I54">
         <v>3.05</v>
@@ -14616,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q54">
         <v>2.14</v>
@@ -15073,7 +15073,7 @@
         <v>2.36</v>
       </c>
       <c r="G56">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H56">
         <v>3.2</v>
@@ -15082,7 +15082,7 @@
         <v>3.3</v>
       </c>
       <c r="J56">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K56">
         <v>3.65</v>
@@ -15312,7 +15312,7 @@
         <v>371</v>
       </c>
       <c r="F57">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G57">
         <v>2.08</v>
@@ -15321,10 +15321,10 @@
         <v>3.8</v>
       </c>
       <c r="I57">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J57">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K57">
         <v>4.2</v>
@@ -15396,7 +15396,7 @@
         <v>13</v>
       </c>
       <c r="AH57">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI57">
         <v>60</v>
@@ -15632,13 +15632,13 @@
         <v>70</v>
       </c>
       <c r="AF58">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG58">
         <v>12.5</v>
       </c>
       <c r="AH58">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI58">
         <v>70</v>
@@ -15811,7 +15811,7 @@
         <v>4.8</v>
       </c>
       <c r="K59">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -15823,13 +15823,13 @@
         <v>5.1</v>
       </c>
       <c r="O59">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P59">
         <v>2.42</v>
       </c>
       <c r="Q59">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R59">
         <v>1.56</v>
@@ -15841,7 +15841,7 @@
         <v>1.8</v>
       </c>
       <c r="U59">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -15850,28 +15850,28 @@
         <v>0</v>
       </c>
       <c r="X59">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y59">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z59">
         <v>70</v>
       </c>
       <c r="AA59">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB59">
         <v>11.5</v>
       </c>
       <c r="AC59">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD59">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE59">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF59">
         <v>11.5</v>
@@ -15880,91 +15880,91 @@
         <v>12</v>
       </c>
       <c r="AH59">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI59">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ59">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK59">
         <v>15.5</v>
       </c>
       <c r="AL59">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM59">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN59">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AO59">
         <v>90</v>
       </c>
       <c r="AP59">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AQ59">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AR59">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AS59">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AT59">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU59">
         <v>9</v>
       </c>
       <c r="AV59">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AW59">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AX59">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AY59">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AZ59">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA59">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BB59">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BC59">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BD59">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE59">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BF59">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BG59">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BH59">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI59">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ59">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK59">
         <v>1.01</v>
@@ -15976,25 +15976,25 @@
         <v>1.01</v>
       </c>
       <c r="BN59">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO59">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP59">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ59">
         <v>1.01</v>
       </c>
       <c r="BR59">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS59">
         <v>1.01</v>
       </c>
       <c r="BT59">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU59">
         <v>1.01</v>
@@ -16006,7 +16006,7 @@
         <v>1.01</v>
       </c>
       <c r="BX59">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY59">
         <v>1.01</v>
@@ -16158,7 +16158,7 @@
         <v>4.6</v>
       </c>
       <c r="AT60">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU60">
         <v>10</v>
@@ -16173,22 +16173,22 @@
         <v>7.4</v>
       </c>
       <c r="AY60">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ60">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA60">
         <v>4.5</v>
       </c>
       <c r="BB60">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC60">
         <v>10</v>
       </c>
       <c r="BD60">
-        <v>4.3</v>
+        <v>22</v>
       </c>
       <c r="BE60">
         <v>4.5</v>
@@ -16531,7 +16531,7 @@
         <v>17.5</v>
       </c>
       <c r="I62">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J62">
         <v>9</v>
@@ -16558,7 +16558,7 @@
         <v>1.39</v>
       </c>
       <c r="R62">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S62">
         <v>1.98</v>
@@ -16567,7 +16567,7 @@
         <v>2.02</v>
       </c>
       <c r="U62">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -16594,7 +16594,7 @@
         <v>21</v>
       </c>
       <c r="AD62">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AE62">
         <v>1000</v>
@@ -16603,7 +16603,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG62">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH62">
         <v>38</v>
@@ -16621,7 +16621,7 @@
         <v>36</v>
       </c>
       <c r="AM62">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN62">
         <v>3.05</v>
@@ -16648,7 +16648,7 @@
         <v>18</v>
       </c>
       <c r="AV62">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AW62">
         <v>95</v>
@@ -16657,7 +16657,7 @@
         <v>8.4</v>
       </c>
       <c r="AY62">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ62">
         <v>30</v>
@@ -16675,13 +16675,13 @@
         <v>29</v>
       </c>
       <c r="BE62">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BF62">
         <v>2.94</v>
       </c>
       <c r="BG62">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BH62">
         <v>5.8</v>
@@ -17006,10 +17006,10 @@
         <v>378</v>
       </c>
       <c r="F64">
+        <v>1.64</v>
+      </c>
+      <c r="G64">
         <v>1.65</v>
-      </c>
-      <c r="G64">
-        <v>1.66</v>
       </c>
       <c r="H64">
         <v>6.2</v>
@@ -17018,7 +17018,7 @@
         <v>6.4</v>
       </c>
       <c r="J64">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K64">
         <v>4.3</v>
@@ -17060,7 +17060,7 @@
         <v>0</v>
       </c>
       <c r="X64">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y64">
         <v>21</v>
@@ -17108,13 +17108,13 @@
         <v>120</v>
       </c>
       <c r="AN64">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO64">
         <v>110</v>
       </c>
       <c r="AP64">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ64">
         <v>18.5</v>
@@ -17135,7 +17135,7 @@
         <v>21</v>
       </c>
       <c r="AW64">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX64">
         <v>8.800000000000001</v>
@@ -17168,7 +17168,7 @@
         <v>40</v>
       </c>
       <c r="BH64">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI64">
         <v>2.96</v>
@@ -17183,49 +17183,49 @@
         <v>140</v>
       </c>
       <c r="BM64">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN64">
         <v>4.4</v>
       </c>
       <c r="BO64">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP64">
         <v>11.5</v>
       </c>
       <c r="BQ64">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BR64">
         <v>27</v>
       </c>
       <c r="BS64">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT64">
         <v>9.800000000000001</v>
       </c>
       <c r="BU64">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BV64">
         <v>55</v>
       </c>
       <c r="BW64">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX64">
         <v>60</v>
       </c>
       <c r="BY64">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ64">
         <v>20</v>
       </c>
       <c r="CA64">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB64" t="s">
         <v>464</v>
@@ -17248,22 +17248,22 @@
         <v>379</v>
       </c>
       <c r="F65">
+        <v>2.38</v>
+      </c>
+      <c r="G65">
         <v>2.4</v>
       </c>
-      <c r="G65">
-        <v>2.44</v>
-      </c>
       <c r="H65">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I65">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J65">
         <v>3.5</v>
       </c>
       <c r="K65">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -17272,28 +17272,28 @@
         <v>1.07</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O65">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P65">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q65">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R65">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S65">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T65">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U65">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -17302,22 +17302,22 @@
         <v>0</v>
       </c>
       <c r="X65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y65">
         <v>13.5</v>
       </c>
       <c r="Z65">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA65">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB65">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC65">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD65">
         <v>14</v>
@@ -17335,31 +17335,31 @@
         <v>16</v>
       </c>
       <c r="AI65">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ65">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK65">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL65">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM65">
         <v>90</v>
       </c>
       <c r="AN65">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO65">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP65">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ65">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR65">
         <v>20</v>
@@ -17371,7 +17371,7 @@
         <v>10</v>
       </c>
       <c r="AU65">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV65">
         <v>12.5</v>
@@ -17383,67 +17383,67 @@
         <v>14</v>
       </c>
       <c r="AY65">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ65">
         <v>14.5</v>
       </c>
       <c r="BA65">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BB65">
+        <v>19.5</v>
+      </c>
+      <c r="BC65">
         <v>21</v>
       </c>
-      <c r="BC65">
-        <v>17</v>
-      </c>
       <c r="BD65">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BE65">
         <v>36</v>
       </c>
       <c r="BF65">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG65">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BH65">
         <v>3.9</v>
       </c>
       <c r="BI65">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ65">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK65">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BL65">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM65">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BN65">
         <v>6</v>
       </c>
       <c r="BO65">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP65">
         <v>20</v>
       </c>
       <c r="BQ65">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR65">
         <v>34</v>
       </c>
       <c r="BS65">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BT65">
         <v>7.4</v>
@@ -17452,22 +17452,22 @@
         <v>5.1</v>
       </c>
       <c r="BV65">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW65">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX65">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY65">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BZ65">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA65">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB65" t="s">
         <v>464</v>
@@ -17735,13 +17735,13 @@
         <v>2.14</v>
       </c>
       <c r="G67">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H67">
         <v>3.05</v>
       </c>
       <c r="I67">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J67">
         <v>3.7</v>
@@ -17977,19 +17977,19 @@
         <v>2.52</v>
       </c>
       <c r="G68">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H68">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I68">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="J68">
         <v>3.75</v>
       </c>
       <c r="K68">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -18219,19 +18219,19 @@
         <v>2.26</v>
       </c>
       <c r="G69">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="H69">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J69">
         <v>3.5</v>
       </c>
       <c r="K69">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -18458,19 +18458,19 @@
         <v>384</v>
       </c>
       <c r="F70">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G70">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H70">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I70">
         <v>3.25</v>
       </c>
       <c r="J70">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="K70">
         <v>4.9</v>
@@ -18488,7 +18488,7 @@
         <v>0</v>
       </c>
       <c r="P70">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q70">
         <v>1.6</v>
@@ -18715,7 +18715,7 @@
         <v>3.35</v>
       </c>
       <c r="K71">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -18733,7 +18733,7 @@
         <v>1.93</v>
       </c>
       <c r="Q71">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -18945,13 +18945,13 @@
         <v>2.54</v>
       </c>
       <c r="G72">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H72">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J72">
         <v>3.6</v>
@@ -18975,7 +18975,7 @@
         <v>1.98</v>
       </c>
       <c r="Q72">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R72">
         <v>1.37</v>
@@ -18984,7 +18984,7 @@
         <v>3.55</v>
       </c>
       <c r="T72">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U72">
         <v>2.2</v>
@@ -19005,7 +19005,7 @@
         <v>21</v>
       </c>
       <c r="AA72">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB72">
         <v>11</v>
@@ -19020,10 +19020,10 @@
         <v>34</v>
       </c>
       <c r="AF72">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG72">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH72">
         <v>17</v>
@@ -19080,16 +19080,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ72">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA72">
         <v>32</v>
       </c>
       <c r="BB72">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC72">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BD72">
         <v>34</v>
@@ -19190,10 +19190,10 @@
         <v>3.25</v>
       </c>
       <c r="H73">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I73">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J73">
         <v>3.6</v>
@@ -19217,7 +19217,7 @@
         <v>2</v>
       </c>
       <c r="Q73">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R73">
         <v>1.38</v>
@@ -19286,7 +19286,7 @@
         <v>90</v>
       </c>
       <c r="AN73">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO73">
         <v>21</v>
@@ -19316,7 +19316,7 @@
         <v>17</v>
       </c>
       <c r="AX73">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY73">
         <v>12</v>
@@ -19328,7 +19328,7 @@
         <v>32</v>
       </c>
       <c r="BB73">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BC73">
         <v>30</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q74">
         <v>2.02</v>
@@ -19668,13 +19668,13 @@
         <v>389</v>
       </c>
       <c r="F75">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G75">
         <v>1.74</v>
       </c>
       <c r="H75">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I75">
         <v>6.6</v>
@@ -20167,7 +20167,7 @@
         <v>4</v>
       </c>
       <c r="K77">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -20182,10 +20182,10 @@
         <v>0</v>
       </c>
       <c r="P77">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="Q77">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -20394,22 +20394,22 @@
         <v>392</v>
       </c>
       <c r="F78">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="G78">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H78">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="I78">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="J78">
         <v>4.3</v>
       </c>
       <c r="K78">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -20424,10 +20424,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q78">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20636,22 +20636,22 @@
         <v>393</v>
       </c>
       <c r="F79">
-        <v>1.78</v>
+        <v>1.1</v>
       </c>
       <c r="G79">
         <v>2</v>
       </c>
       <c r="H79">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I79">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J79">
         <v>4.4</v>
       </c>
       <c r="K79">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>2.56</v>
       </c>
       <c r="Q79">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20878,40 +20878,40 @@
         <v>394</v>
       </c>
       <c r="F80">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G80">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H80">
+        <v>5.2</v>
+      </c>
+      <c r="I80">
+        <v>7</v>
+      </c>
+      <c r="J80">
+        <v>4.2</v>
+      </c>
+      <c r="K80">
+        <v>5.4</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
         <v>2.34</v>
       </c>
-      <c r="I80">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J80">
-        <v>3.9</v>
-      </c>
-      <c r="K80">
-        <v>210</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>2.28</v>
-      </c>
       <c r="Q80">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -21126,7 +21126,7 @@
         <v>1000</v>
       </c>
       <c r="H81">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I81">
         <v>1000</v>
@@ -21401,7 +21401,7 @@
         <v>1.53</v>
       </c>
       <c r="S82">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T82">
         <v>1.86</v>
@@ -21524,55 +21524,55 @@
         <v>10.5</v>
       </c>
       <c r="BH82">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI82">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ82">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK82">
         <v>1.01</v>
       </c>
       <c r="BL82">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM82">
         <v>1.01</v>
       </c>
       <c r="BN82">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO82">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP82">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ82">
         <v>1.01</v>
       </c>
       <c r="BR82">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS82">
         <v>1.01</v>
       </c>
       <c r="BT82">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU82">
         <v>1.01</v>
       </c>
       <c r="BV82">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW82">
         <v>1.01</v>
       </c>
       <c r="BX82">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY82">
         <v>1.01</v>
@@ -21604,7 +21604,7 @@
         <v>397</v>
       </c>
       <c r="F83">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G83">
         <v>2.22</v>
@@ -21619,7 +21619,7 @@
         <v>3.8</v>
       </c>
       <c r="K83">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -21637,7 +21637,7 @@
         <v>2.34</v>
       </c>
       <c r="Q83">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -21849,16 +21849,16 @@
         <v>2.24</v>
       </c>
       <c r="G84">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H84">
         <v>3</v>
       </c>
       <c r="I84">
+        <v>3.4</v>
+      </c>
+      <c r="J84">
         <v>3.6</v>
-      </c>
-      <c r="J84">
-        <v>3.55</v>
       </c>
       <c r="K84">
         <v>4.6</v>
@@ -21879,7 +21879,7 @@
         <v>2.16</v>
       </c>
       <c r="Q84">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>0</v>
       </c>
       <c r="P86">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q86">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -22575,10 +22575,10 @@
         <v>2.34</v>
       </c>
       <c r="G87">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H87">
-        <v>1.57</v>
+        <v>2.78</v>
       </c>
       <c r="I87">
         <v>3.45</v>
@@ -22587,7 +22587,7 @@
         <v>3.55</v>
       </c>
       <c r="K87">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -22602,10 +22602,10 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q87">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>1.87</v>
       </c>
       <c r="H88">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I88">
         <v>4.8</v>
@@ -22859,7 +22859,7 @@
         <v>1.66</v>
       </c>
       <c r="U88">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V88">
         <v>0</v>
@@ -23071,7 +23071,7 @@
         <v>5.4</v>
       </c>
       <c r="K89">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>404</v>
       </c>
       <c r="F90">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="G90">
         <v>1.96</v>
@@ -23331,7 +23331,7 @@
         <v>2.72</v>
       </c>
       <c r="Q90">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -23343,7 +23343,7 @@
         <v>1.54</v>
       </c>
       <c r="U90">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V90">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>405</v>
       </c>
       <c r="F91">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G91">
         <v>1.7</v>
@@ -23573,7 +23573,7 @@
         <v>1.87</v>
       </c>
       <c r="Q91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R91">
         <v>1.33</v>
@@ -23782,10 +23782,10 @@
         <v>406</v>
       </c>
       <c r="F92">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G92">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H92">
         <v>2.54</v>
@@ -23797,7 +23797,7 @@
         <v>4</v>
       </c>
       <c r="K92">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -23815,7 +23815,7 @@
         <v>2.68</v>
       </c>
       <c r="Q92">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -24024,22 +24024,22 @@
         <v>407</v>
       </c>
       <c r="F93">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="G93">
-        <v>10</v>
+        <v>1.68</v>
       </c>
       <c r="H93">
-        <v>1.12</v>
+        <v>4.4</v>
       </c>
       <c r="I93">
         <v>1000</v>
       </c>
       <c r="J93">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="K93">
-        <v>220</v>
+        <v>10.5</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -24054,10 +24054,10 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q93">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -24296,10 +24296,10 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q94">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -24508,22 +24508,22 @@
         <v>409</v>
       </c>
       <c r="F95">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="G95">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H95">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="I95">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="J95">
         <v>4</v>
       </c>
       <c r="K95">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -24541,7 +24541,7 @@
         <v>2</v>
       </c>
       <c r="Q95">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -24750,22 +24750,22 @@
         <v>410</v>
       </c>
       <c r="F96">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="G96">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H96">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="I96">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="J96">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K96">
-        <v>310</v>
+        <v>4.2</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -24780,10 +24780,10 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q96">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -25001,10 +25001,10 @@
         <v>17.5</v>
       </c>
       <c r="I97">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J97">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="K97">
         <v>10.5</v>
@@ -25022,10 +25022,10 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q97">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -25243,7 +25243,7 @@
         <v>3.2</v>
       </c>
       <c r="I98">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J98">
         <v>3.8</v>
@@ -25264,10 +25264,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q98">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -25718,22 +25718,22 @@
         <v>414</v>
       </c>
       <c r="F100">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="G100">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="H100">
-        <v>9</v>
+        <v>1.13</v>
       </c>
       <c r="I100">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J100">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="K100">
-        <v>270</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -25748,10 +25748,10 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q100">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -25960,22 +25960,22 @@
         <v>415</v>
       </c>
       <c r="F101">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G101">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H101">
+        <v>3.4</v>
+      </c>
+      <c r="I101">
         <v>3.45</v>
-      </c>
-      <c r="I101">
-        <v>3.5</v>
       </c>
       <c r="J101">
         <v>3.5</v>
       </c>
       <c r="K101">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -26104,7 +26104,7 @@
         <v>36</v>
       </c>
       <c r="BB101">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC101">
         <v>20</v>
@@ -26444,10 +26444,10 @@
         <v>417</v>
       </c>
       <c r="F103">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="G103">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H103">
         <v>1.17</v>
@@ -26480,7 +26480,7 @@
         <v>1.27</v>
       </c>
       <c r="R103">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S103">
         <v>1.7</v>
@@ -26573,13 +26573,13 @@
         <v>12.5</v>
       </c>
       <c r="AW103">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX103">
         <v>48</v>
       </c>
       <c r="AY103">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AZ103">
         <v>30</v>
@@ -26591,7 +26591,7 @@
         <v>18.5</v>
       </c>
       <c r="BC103">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD103">
         <v>44</v>
@@ -26606,55 +26606,55 @@
         <v>2.38</v>
       </c>
       <c r="BH103">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI103">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BJ103">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK103">
         <v>1.01</v>
       </c>
       <c r="BL103">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM103">
         <v>1.01</v>
       </c>
       <c r="BN103">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BO103">
         <v>1.01</v>
       </c>
       <c r="BP103">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BQ103">
         <v>1.01</v>
       </c>
       <c r="BR103">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS103">
         <v>1.01</v>
       </c>
       <c r="BT103">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU103">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV103">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BW103">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX103">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY103">
         <v>1.01</v>
@@ -26686,13 +26686,13 @@
         <v>418</v>
       </c>
       <c r="F104">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G104">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H104">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I104">
         <v>1.96</v>
@@ -26701,7 +26701,7 @@
         <v>3.9</v>
       </c>
       <c r="K104">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -26722,7 +26722,7 @@
         <v>1.93</v>
       </c>
       <c r="R104">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S104">
         <v>3.4</v>
@@ -26752,7 +26752,7 @@
         <v>22</v>
       </c>
       <c r="AB104">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC104">
         <v>8.4</v>
@@ -26767,22 +26767,22 @@
         <v>30</v>
       </c>
       <c r="AG104">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH104">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI104">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ104">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK104">
         <v>55</v>
       </c>
       <c r="AL104">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM104">
         <v>110</v>
@@ -26812,19 +26812,19 @@
         <v>7.8</v>
       </c>
       <c r="AV104">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW104">
         <v>18</v>
       </c>
       <c r="AX104">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AY104">
         <v>15.5</v>
       </c>
       <c r="AZ104">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA104">
         <v>23</v>
@@ -26839,7 +26839,7 @@
         <v>30</v>
       </c>
       <c r="BE104">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF104">
         <v>29</v>
@@ -26848,64 +26848,64 @@
         <v>11.5</v>
       </c>
       <c r="BH104">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI104">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ104">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK104">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BL104">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM104">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN104">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO104">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP104">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ104">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR104">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS104">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT104">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU104">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV104">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW104">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX104">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY104">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ104">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA104">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB104" t="s">
         <v>464</v>
@@ -26928,10 +26928,10 @@
         <v>419</v>
       </c>
       <c r="F105">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G105">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H105">
         <v>3.1</v>
@@ -27182,7 +27182,7 @@
         <v>5</v>
       </c>
       <c r="J106">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K106">
         <v>5.4</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="Q106">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -27418,7 +27418,7 @@
         <v>2.18</v>
       </c>
       <c r="H107">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I107">
         <v>3.6</v>
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="T109">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U109">
         <v>1.95</v>
@@ -28380,22 +28380,22 @@
         <v>425</v>
       </c>
       <c r="F111">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G111">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="H111">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="I111">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J111">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K111">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -28410,10 +28410,10 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q111">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -28622,13 +28622,13 @@
         <v>426</v>
       </c>
       <c r="F112">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G112">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H112">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I112">
         <v>6.2</v>
@@ -28652,10 +28652,10 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q112">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -28870,13 +28870,13 @@
         <v>15</v>
       </c>
       <c r="H113">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I113">
         <v>1.29</v>
       </c>
       <c r="J113">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K113">
         <v>6.8</v>
@@ -29106,22 +29106,22 @@
         <v>428</v>
       </c>
       <c r="F114">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G114">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H114">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I114">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="J114">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K114">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -29139,7 +29139,7 @@
         <v>1.75</v>
       </c>
       <c r="Q114">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -29841,10 +29841,10 @@
         <v>3.45</v>
       </c>
       <c r="I117">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J117">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="K117">
         <v>4.7</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q117">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -30080,10 +30080,10 @@
         <v>3</v>
       </c>
       <c r="H118">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I118">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J118">
         <v>2.9</v>
@@ -30316,22 +30316,22 @@
         <v>433</v>
       </c>
       <c r="F119">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G119">
         <v>1.69</v>
       </c>
       <c r="H119">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I119">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="J119">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K119">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -30346,10 +30346,10 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q119">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -31057,7 +31057,7 @@
         <v>4.2</v>
       </c>
       <c r="K122">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -31072,7 +31072,7 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q122">
         <v>1.34</v>
@@ -31290,7 +31290,7 @@
         <v>2.18</v>
       </c>
       <c r="H123">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="I123">
         <v>4.5</v>
@@ -31299,7 +31299,7 @@
         <v>3.95</v>
       </c>
       <c r="K123">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -31535,10 +31535,10 @@
         <v>1.56</v>
       </c>
       <c r="I124">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J124">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K124">
         <v>5.7</v>
@@ -31771,19 +31771,19 @@
         <v>2.54</v>
       </c>
       <c r="G125">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H125">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I125">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="J125">
         <v>2.86</v>
       </c>
       <c r="K125">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -32010,22 +32010,22 @@
         <v>440</v>
       </c>
       <c r="F126">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="G126">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="H126">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="I126">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="J126">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K126">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -32040,10 +32040,10 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q126">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -32252,22 +32252,22 @@
         <v>441</v>
       </c>
       <c r="F127">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="G127">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="H127">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I127">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="J127">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K127">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L127">
         <v>0</v>
@@ -32282,10 +32282,10 @@
         <v>0</v>
       </c>
       <c r="P127">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="Q127">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -32978,22 +32978,22 @@
         <v>444</v>
       </c>
       <c r="F130">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G130">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H130">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="I130">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J130">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K130">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -33008,10 +33008,10 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q130">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -33704,7 +33704,7 @@
         <v>447</v>
       </c>
       <c r="F133">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G133">
         <v>2.3</v>
@@ -33713,7 +33713,7 @@
         <v>3.2</v>
       </c>
       <c r="I133">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J133">
         <v>3.75</v>
@@ -33734,10 +33734,10 @@
         <v>0</v>
       </c>
       <c r="P133">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q133">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -34430,7 +34430,7 @@
         <v>450</v>
       </c>
       <c r="F136">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G136">
         <v>2.86</v>
@@ -34463,7 +34463,7 @@
         <v>1.79</v>
       </c>
       <c r="Q136">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R136">
         <v>1.29</v>
@@ -34592,55 +34592,55 @@
         <v>8</v>
       </c>
       <c r="BH136">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI136">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ136">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK136">
         <v>1.01</v>
       </c>
       <c r="BL136">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM136">
         <v>1.01</v>
       </c>
       <c r="BN136">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO136">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP136">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ136">
         <v>1.01</v>
       </c>
       <c r="BR136">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS136">
         <v>1.01</v>
       </c>
       <c r="BT136">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU136">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV136">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW136">
         <v>1.01</v>
       </c>
       <c r="BX136">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY136">
         <v>1.01</v>
@@ -34786,10 +34786,10 @@
         <v>14</v>
       </c>
       <c r="AR137">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS137">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT137">
         <v>8.199999999999999</v>
@@ -34914,7 +34914,7 @@
         <v>452</v>
       </c>
       <c r="F138">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G138">
         <v>1.78</v>
@@ -34944,10 +34944,10 @@
         <v>1.33</v>
       </c>
       <c r="P138">
+        <v>1.97</v>
+      </c>
+      <c r="Q138">
         <v>1.96</v>
-      </c>
-      <c r="Q138">
-        <v>1.97</v>
       </c>
       <c r="R138">
         <v>1.37</v>
@@ -34956,7 +34956,7 @@
         <v>3.5</v>
       </c>
       <c r="T138">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U138">
         <v>2.02</v>
@@ -35001,7 +35001,7 @@
         <v>21</v>
       </c>
       <c r="AI138">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ138">
         <v>18</v>
@@ -35019,7 +35019,7 @@
         <v>11</v>
       </c>
       <c r="AO138">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP138">
         <v>13.5</v>
@@ -35049,7 +35049,7 @@
         <v>9.4</v>
       </c>
       <c r="AY138">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ138">
         <v>18.5</v>
@@ -35076,58 +35076,58 @@
         <v>36</v>
       </c>
       <c r="BH138">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI138">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ138">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK138">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL138">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM138">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN138">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO138">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP138">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ138">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR138">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS138">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT138">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU138">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV138">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW138">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX138">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY138">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ138">
         <v>0</v>
@@ -35156,22 +35156,22 @@
         <v>453</v>
       </c>
       <c r="F139">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G139">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H139">
         <v>4.4</v>
       </c>
       <c r="I139">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J139">
         <v>4</v>
       </c>
       <c r="K139">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L139">
         <v>1.01</v>
@@ -35882,19 +35882,19 @@
         <v>456</v>
       </c>
       <c r="F142">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G142">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H142">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I142">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="J142">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K142">
         <v>3.75</v>
@@ -36157,7 +36157,7 @@
         <v>2.4</v>
       </c>
       <c r="Q143">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -36372,16 +36372,16 @@
         <v>7.8</v>
       </c>
       <c r="H144">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I144">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J144">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K144">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -36390,28 +36390,28 @@
         <v>1.02</v>
       </c>
       <c r="N144">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O144">
         <v>1.17</v>
       </c>
       <c r="P144">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q144">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="R144">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S144">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T144">
         <v>1.7</v>
       </c>
       <c r="U144">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V144">
         <v>0</v>
@@ -36420,7 +36420,7 @@
         <v>0</v>
       </c>
       <c r="X144">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y144">
         <v>12.5</v>
@@ -36444,7 +36444,7 @@
         <v>15</v>
       </c>
       <c r="AF144">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG144">
         <v>28</v>
@@ -36462,13 +36462,13 @@
         <v>90</v>
       </c>
       <c r="AL144">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM144">
         <v>95</v>
       </c>
       <c r="AN144">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO144">
         <v>5.6</v>
@@ -36498,10 +36498,10 @@
         <v>12</v>
       </c>
       <c r="AX144">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY144">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AZ144">
         <v>16.5</v>
@@ -36510,31 +36510,31 @@
         <v>7</v>
       </c>
       <c r="BB144">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC144">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD144">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE144">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF144">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG144">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH144">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI144">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ144">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK144">
         <v>1.01</v>
@@ -36546,37 +36546,37 @@
         <v>1.01</v>
       </c>
       <c r="BN144">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO144">
         <v>1.01</v>
       </c>
       <c r="BP144">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ144">
         <v>1.01</v>
       </c>
       <c r="BR144">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS144">
         <v>1.01</v>
       </c>
       <c r="BT144">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU144">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV144">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW144">
         <v>1.01</v>
       </c>
       <c r="BX144">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY144">
         <v>1.01</v>
@@ -36608,7 +36608,7 @@
         <v>459</v>
       </c>
       <c r="F145">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G145">
         <v>1.55</v>
@@ -36620,7 +36620,7 @@
         <v>7.2</v>
       </c>
       <c r="J145">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K145">
         <v>4.9</v>
@@ -36743,7 +36743,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY145">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ145">
         <v>20</v>
@@ -36770,64 +36770,64 @@
         <v>38</v>
       </c>
       <c r="BH145">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI145">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ145">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK145">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL145">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM145">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN145">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO145">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP145">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ145">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR145">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS145">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT145">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU145">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV145">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW145">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX145">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY145">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BZ145">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA145">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB145" t="s">
         <v>464</v>
@@ -36850,22 +36850,22 @@
         <v>460</v>
       </c>
       <c r="F146">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G146">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="H146">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="I146">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J146">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K146">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -37349,7 +37349,7 @@
         <v>1.08</v>
       </c>
       <c r="K148">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="L148">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-05.xlsx
@@ -2026,7 +2026,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-09-03 20:55:54</t>
+    <t>2026-09-03 23:20:00</t>
   </si>
 </sst>
 </file>
@@ -2668,7 +2668,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
         <v>1.5</v>
@@ -2862,10 +2862,10 @@
         <v>434</v>
       </c>
       <c r="F3">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G3">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="H3">
         <v>5.7</v>
@@ -2874,19 +2874,19 @@
         <v>10.5</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
         <v>1.3</v>
@@ -2895,13 +2895,13 @@
         <v>2</v>
       </c>
       <c r="Q3">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="T3">
         <v>1.87</v>
@@ -2910,10 +2910,10 @@
         <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -3104,7 +3104,7 @@
         <v>435</v>
       </c>
       <c r="F4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G4">
         <v>2.1</v>
@@ -3152,7 +3152,7 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
         <v>1.9</v>
@@ -3346,7 +3346,7 @@
         <v>436</v>
       </c>
       <c r="F5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G5">
         <v>4.1</v>
@@ -3376,7 +3376,7 @@
         <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q5">
         <v>2.16</v>
@@ -3588,7 +3588,7 @@
         <v>437</v>
       </c>
       <c r="F6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>5.1</v>
@@ -3600,7 +3600,7 @@
         <v>2.18</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
         <v>3.65</v>
@@ -3618,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="Q6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -3830,49 +3830,49 @@
         <v>438</v>
       </c>
       <c r="F7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>6.4</v>
       </c>
       <c r="H7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
         <v>5.2</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="T7">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U7">
         <v>2.34</v>
@@ -4314,13 +4314,13 @@
         <v>440</v>
       </c>
       <c r="F9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I9">
         <v>2.2</v>
@@ -4350,10 +4350,10 @@
         <v>1.92</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T9">
         <v>1.77</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="AF9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG9">
         <v>17</v>
@@ -4425,7 +4425,7 @@
         <v>12</v>
       </c>
       <c r="AQ9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR9">
         <v>10.5</v>
@@ -4443,7 +4443,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
         <v>6.4</v>
@@ -4455,19 +4455,19 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC9">
         <v>34</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9">
         <v>36</v>
@@ -5073,7 +5073,7 @@
         <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -5306,22 +5306,22 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="R13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T13">
         <v>1.64</v>
@@ -5524,13 +5524,13 @@
         <v>445</v>
       </c>
       <c r="F14">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="G14">
         <v>2.44</v>
       </c>
       <c r="H14">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="I14">
         <v>4.1</v>
@@ -5539,31 +5539,31 @@
         <v>3.25</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O14">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P14">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="R14">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T14">
         <v>1.92</v>
@@ -5572,7 +5572,7 @@
         <v>1.94</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
         <v>1.7</v>
@@ -5775,10 +5775,10 @@
         <v>4.3</v>
       </c>
       <c r="I15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J15">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K15">
         <v>3.8</v>
@@ -5802,13 +5802,13 @@
         <v>2.06</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S15">
         <v>3.7</v>
       </c>
       <c r="T15">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U15">
         <v>2.02</v>
@@ -5835,19 +5835,19 @@
         <v>9.4</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD15">
         <v>21</v>
       </c>
       <c r="AE15">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AF15">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH15">
         <v>24</v>
@@ -5883,7 +5883,7 @@
         <v>19.5</v>
       </c>
       <c r="AS15">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AT15">
         <v>7.6</v>
@@ -5892,7 +5892,7 @@
         <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW15">
         <v>29</v>
@@ -5901,7 +5901,7 @@
         <v>10.5</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15">
         <v>17.5</v>
@@ -5916,10 +5916,10 @@
         <v>15</v>
       </c>
       <c r="BD15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE15">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF15">
         <v>13.5</v>
@@ -6507,7 +6507,7 @@
         <v>3.5</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>1.31</v>
@@ -6543,7 +6543,7 @@
         <v>1.8</v>
       </c>
       <c r="W18">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -6764,7 +6764,7 @@
         <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
         <v>1.68</v>
@@ -6976,22 +6976,22 @@
         <v>451</v>
       </c>
       <c r="F20">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="G20">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H20">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I20">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J20">
         <v>3.3</v>
       </c>
       <c r="K20">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -7015,7 +7015,7 @@
         <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -7218,10 +7218,10 @@
         <v>452</v>
       </c>
       <c r="F21">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G21">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H21">
         <v>4.6</v>
@@ -7230,7 +7230,7 @@
         <v>5</v>
       </c>
       <c r="J21">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
         <v>3.8</v>
@@ -7248,31 +7248,31 @@
         <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q21">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R21">
         <v>1.3</v>
       </c>
       <c r="S21">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T21">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U21">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V21">
         <v>1.25</v>
       </c>
       <c r="W21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y21">
         <v>18.5</v>
@@ -7284,10 +7284,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21">
         <v>24</v>
@@ -7335,16 +7335,16 @@
         <v>21</v>
       </c>
       <c r="AS21">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AT21">
         <v>7.2</v>
       </c>
       <c r="AU21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV21">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW21">
         <v>32</v>
@@ -7371,13 +7371,13 @@
         <v>26</v>
       </c>
       <c r="BE21">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BF21">
         <v>13</v>
       </c>
       <c r="BG21">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH21">
         <v>3.85</v>
@@ -7705,19 +7705,19 @@
         <v>3.1</v>
       </c>
       <c r="G23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I23">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -7726,7 +7726,7 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
         <v>1.29</v>
@@ -7735,19 +7735,19 @@
         <v>2.06</v>
       </c>
       <c r="Q23">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S23">
         <v>3.15</v>
       </c>
       <c r="T23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
         <v>1.69</v>
@@ -7759,7 +7759,7 @@
         <v>20</v>
       </c>
       <c r="Y23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z23">
         <v>20</v>
@@ -7771,7 +7771,7 @@
         <v>17</v>
       </c>
       <c r="AC23">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
         <v>14</v>
@@ -7855,7 +7855,7 @@
         <v>25</v>
       </c>
       <c r="BE23">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF23">
         <v>24</v>
@@ -8186,7 +8186,7 @@
         <v>456</v>
       </c>
       <c r="F25">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25">
         <v>2.64</v>
@@ -8195,7 +8195,7 @@
         <v>3.25</v>
       </c>
       <c r="I25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J25">
         <v>3.1</v>
@@ -8207,25 +8207,25 @@
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N25">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="O25">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="P25">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q25">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="R25">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S25">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T25">
         <v>1.96</v>
@@ -8428,7 +8428,7 @@
         <v>457</v>
       </c>
       <c r="F26">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G26">
         <v>2.64</v>
@@ -8449,31 +8449,31 @@
         <v>1.36</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
         <v>1.39</v>
       </c>
       <c r="P26">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="Q26">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S26">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="T26">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U26">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V26">
         <v>1.38</v>
@@ -8673,19 +8673,19 @@
         <v>4.3</v>
       </c>
       <c r="G27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I27">
         <v>2.02</v>
       </c>
       <c r="J27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
         <v>1.36</v>
@@ -8694,34 +8694,34 @@
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
         <v>1.83</v>
       </c>
       <c r="Q27">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V27">
         <v>1.98</v>
       </c>
       <c r="W27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X27">
         <v>17</v>
@@ -8775,7 +8775,7 @@
         <v>85</v>
       </c>
       <c r="AO27">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AP27">
         <v>12</v>
@@ -8802,7 +8802,7 @@
         <v>15.5</v>
       </c>
       <c r="AX27">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AY27">
         <v>15.5</v>
@@ -8811,22 +8811,22 @@
         <v>16.5</v>
       </c>
       <c r="BA27">
+        <v>5.1</v>
+      </c>
+      <c r="BB27">
+        <v>5.5</v>
+      </c>
+      <c r="BC27">
+        <v>5.3</v>
+      </c>
+      <c r="BD27">
+        <v>5.3</v>
+      </c>
+      <c r="BE27">
+        <v>5.5</v>
+      </c>
+      <c r="BF27">
         <v>5.4</v>
-      </c>
-      <c r="BB27">
-        <v>5.7</v>
-      </c>
-      <c r="BC27">
-        <v>5.6</v>
-      </c>
-      <c r="BD27">
-        <v>5.6</v>
-      </c>
-      <c r="BE27">
-        <v>5.6</v>
-      </c>
-      <c r="BF27">
-        <v>5.7</v>
       </c>
       <c r="BG27">
         <v>12.5</v>
@@ -8927,7 +8927,7 @@
         <v>3.3</v>
       </c>
       <c r="K28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L28">
         <v>1.37</v>
@@ -8936,7 +8936,7 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O28">
         <v>1.41</v>
@@ -8945,13 +8945,13 @@
         <v>1.67</v>
       </c>
       <c r="Q28">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="R28">
         <v>1.18</v>
       </c>
       <c r="S28">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -9396,16 +9396,16 @@
         <v>461</v>
       </c>
       <c r="F30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G30">
         <v>2.14</v>
       </c>
       <c r="H30">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J30">
         <v>3.45</v>
@@ -9420,10 +9420,10 @@
         <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P30">
         <v>1.83</v>
@@ -9432,28 +9432,28 @@
         <v>2.12</v>
       </c>
       <c r="R30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S30">
         <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
         <v>1.87</v>
       </c>
       <c r="X30">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y30">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z30">
         <v>32</v>
@@ -9462,25 +9462,25 @@
         <v>100</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC30">
         <v>8.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE30">
         <v>65</v>
       </c>
       <c r="AF30">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG30">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30">
         <v>75</v>
@@ -9498,64 +9498,64 @@
         <v>130</v>
       </c>
       <c r="AN30">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO30">
         <v>70</v>
       </c>
       <c r="AP30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ30">
         <v>11.5</v>
       </c>
       <c r="AR30">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS30">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT30">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU30">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV30">
         <v>14</v>
       </c>
       <c r="AW30">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30">
         <v>16.5</v>
       </c>
       <c r="BA30">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BB30">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BC30">
         <v>20</v>
       </c>
       <c r="BD30">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE30">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF30">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG30">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -10131,7 +10131,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -10146,7 +10146,7 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O33">
         <v>1.14</v>
@@ -10155,22 +10155,22 @@
         <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R33">
         <v>1.87</v>
       </c>
       <c r="S33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T33">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V33">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W33">
         <v>3.85</v>
@@ -10236,10 +10236,10 @@
         <v>40</v>
       </c>
       <c r="AR33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT33">
         <v>12</v>
@@ -10251,7 +10251,7 @@
         <v>32</v>
       </c>
       <c r="AW33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX33">
         <v>9.4</v>
@@ -10275,13 +10275,13 @@
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BF33">
         <v>3.6</v>
       </c>
       <c r="BG33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -10364,31 +10364,31 @@
         <v>465</v>
       </c>
       <c r="F34">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G34">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H34">
         <v>4.2</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J34">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K34">
         <v>3.8</v>
       </c>
       <c r="L34">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M34">
         <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O34">
         <v>1.32</v>
@@ -10397,28 +10397,28 @@
         <v>1.93</v>
       </c>
       <c r="Q34">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S34">
         <v>3.3</v>
       </c>
       <c r="T34">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U34">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X34">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y34">
         <v>23</v>
@@ -10433,7 +10433,7 @@
         <v>9.4</v>
       </c>
       <c r="AC34">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34">
         <v>18</v>
@@ -10475,13 +10475,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ34">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR34">
         <v>19</v>
       </c>
       <c r="AS34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT34">
         <v>8.199999999999999</v>
@@ -10490,13 +10490,13 @@
         <v>7.2</v>
       </c>
       <c r="AV34">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW34">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX34">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY34">
         <v>9.199999999999999</v>
@@ -10505,25 +10505,25 @@
         <v>15.5</v>
       </c>
       <c r="BA34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB34">
         <v>14</v>
       </c>
       <c r="BC34">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD34">
         <v>22</v>
       </c>
       <c r="BE34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF34">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BG34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -10606,16 +10606,16 @@
         <v>466</v>
       </c>
       <c r="F35">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G35">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I35">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J35">
         <v>3.8</v>
@@ -10630,37 +10630,37 @@
         <v>1.05</v>
       </c>
       <c r="N35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O35">
         <v>1.23</v>
       </c>
       <c r="P35">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q35">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R35">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S35">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T35">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U35">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="V35">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y35">
         <v>18</v>
@@ -10672,10 +10672,10 @@
         <v>60</v>
       </c>
       <c r="AB35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC35">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35">
         <v>16.5</v>
@@ -10717,16 +10717,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR35">
         <v>20</v>
       </c>
       <c r="AS35">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU35">
         <v>7.8</v>
@@ -10735,22 +10735,22 @@
         <v>12</v>
       </c>
       <c r="AW35">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX35">
         <v>14</v>
       </c>
       <c r="AY35">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ35">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA35">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB35">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC35">
         <v>19</v>
@@ -10759,10 +10759,10 @@
         <v>21</v>
       </c>
       <c r="BE35">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG35">
         <v>19</v>
@@ -10848,49 +10848,49 @@
         <v>467</v>
       </c>
       <c r="F36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G36">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H36">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>3.05</v>
       </c>
       <c r="J36">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K36">
         <v>3.95</v>
       </c>
       <c r="L36">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
         <v>1.04</v>
       </c>
       <c r="N36">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O36">
         <v>1.21</v>
       </c>
       <c r="P36">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q36">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R36">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S36">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T36">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U36">
         <v>2.62</v>
@@ -10899,7 +10899,7 @@
         <v>1.48</v>
       </c>
       <c r="W36">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X36">
         <v>23</v>
@@ -10950,7 +10950,7 @@
         <v>65</v>
       </c>
       <c r="AN36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO36">
         <v>23</v>
@@ -10977,7 +10977,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36">
-        <v>25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX36">
         <v>16</v>
@@ -10989,7 +10989,7 @@
         <v>13</v>
       </c>
       <c r="BA36">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB36">
         <v>29</v>
@@ -11010,64 +11010,64 @@
         <v>16.5</v>
       </c>
       <c r="BH36">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL36">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM36">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP36">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR36">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV36">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX36">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY36">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="s">
         <v>670</v>
@@ -11090,19 +11090,19 @@
         <v>468</v>
       </c>
       <c r="F37">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H37">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I37">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="J37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K37">
         <v>4.1</v>
@@ -11120,7 +11120,7 @@
         <v>1.18</v>
       </c>
       <c r="P37">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
         <v>1.54</v>
@@ -11132,16 +11132,16 @@
         <v>2.36</v>
       </c>
       <c r="T37">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="U37">
         <v>2.42</v>
       </c>
       <c r="V37">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W37">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X37">
         <v>29</v>
@@ -11183,7 +11183,7 @@
         <v>60</v>
       </c>
       <c r="AK37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL37">
         <v>36</v>
@@ -11198,7 +11198,7 @@
         <v>11.5</v>
       </c>
       <c r="AP37">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ37">
         <v>11.5</v>
@@ -11210,31 +11210,31 @@
         <v>21</v>
       </c>
       <c r="AT37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU37">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV37">
         <v>9</v>
       </c>
       <c r="AW37">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX37">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY37">
         <v>11</v>
       </c>
       <c r="AZ37">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BA37">
         <v>20</v>
       </c>
       <c r="BB37">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC37">
         <v>5.3</v>
@@ -11246,10 +11246,10 @@
         <v>5.7</v>
       </c>
       <c r="BF37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG37">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -11359,13 +11359,13 @@
         <v>4.2</v>
       </c>
       <c r="O38">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P38">
         <v>2.14</v>
       </c>
       <c r="Q38">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R38">
         <v>1.44</v>
@@ -11574,7 +11574,7 @@
         <v>470</v>
       </c>
       <c r="F39">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G39">
         <v>3.3</v>
@@ -11589,10 +11589,10 @@
         <v>3.05</v>
       </c>
       <c r="K39">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L39">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
         <v>1.04</v>
@@ -11601,25 +11601,25 @@
         <v>3.7</v>
       </c>
       <c r="O39">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P39">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R39">
         <v>1.36</v>
       </c>
       <c r="S39">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T39">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U39">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V39">
         <v>1.49</v>
@@ -11816,22 +11816,22 @@
         <v>471</v>
       </c>
       <c r="F40">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G40">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H40">
         <v>3.75</v>
       </c>
       <c r="I40">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J40">
+        <v>3.35</v>
+      </c>
+      <c r="K40">
         <v>3.45</v>
-      </c>
-      <c r="K40">
-        <v>3.5</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -11852,22 +11852,22 @@
         <v>2.2</v>
       </c>
       <c r="R40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S40">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T40">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U40">
         <v>2</v>
       </c>
       <c r="V40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W40">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X40">
         <v>12</v>
@@ -11891,7 +11891,7 @@
         <v>15.5</v>
       </c>
       <c r="AE40">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF40">
         <v>13</v>
@@ -11918,10 +11918,10 @@
         <v>130</v>
       </c>
       <c r="AN40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO40">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP40">
         <v>10.5</v>
@@ -11930,7 +11930,7 @@
         <v>11.5</v>
       </c>
       <c r="AR40">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AS40">
         <v>32</v>
@@ -11948,7 +11948,7 @@
         <v>44</v>
       </c>
       <c r="AX40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY40">
         <v>10</v>
@@ -11975,13 +11975,13 @@
         <v>18.5</v>
       </c>
       <c r="BG40">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BH40">
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
@@ -12106,7 +12106,7 @@
         <v>2.28</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
         <v>1.7</v>
@@ -12309,10 +12309,10 @@
         <v>1.86</v>
       </c>
       <c r="I42">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J42">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K42">
         <v>4.3</v>
@@ -12342,13 +12342,13 @@
         <v>2.86</v>
       </c>
       <c r="T42">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V42">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W42">
         <v>1.29</v>
@@ -12381,7 +12381,7 @@
         <v>36</v>
       </c>
       <c r="AG42">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH42">
         <v>17.5</v>
@@ -12414,7 +12414,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS42">
         <v>19</v>
@@ -12623,7 +12623,7 @@
         <v>16.5</v>
       </c>
       <c r="AG43">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH43">
         <v>14</v>
@@ -12737,7 +12737,7 @@
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>2.12</v>
+        <v>1.49</v>
       </c>
       <c r="BT43">
         <v>970</v>
@@ -12787,7 +12787,7 @@
         <v>1.61</v>
       </c>
       <c r="G44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H44">
         <v>5.4</v>
@@ -12799,13 +12799,13 @@
         <v>4.1</v>
       </c>
       <c r="K44">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44">
         <v>1.01</v>
       </c>
       <c r="M44">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -12823,7 +12823,7 @@
         <v>1.41</v>
       </c>
       <c r="S44">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T44">
         <v>1.82</v>
@@ -12832,16 +12832,16 @@
         <v>1.99</v>
       </c>
       <c r="V44">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W44">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X44">
         <v>22</v>
       </c>
       <c r="Y44">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z44">
         <v>60</v>
@@ -13050,13 +13050,13 @@
         <v>1.07</v>
       </c>
       <c r="N45">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O45">
         <v>1.35</v>
       </c>
       <c r="P45">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q45">
         <v>2.04</v>
@@ -13065,7 +13065,7 @@
         <v>1.34</v>
       </c>
       <c r="S45">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T45">
         <v>1.81</v>
@@ -13122,16 +13122,16 @@
         <v>32</v>
       </c>
       <c r="AL45">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM45">
         <v>1000</v>
       </c>
       <c r="AN45">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO45">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP45">
         <v>11.5</v>
@@ -13146,7 +13146,7 @@
         <v>27</v>
       </c>
       <c r="AT45">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -13271,19 +13271,19 @@
         <v>1.46</v>
       </c>
       <c r="G46">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H46">
         <v>7</v>
       </c>
       <c r="I46">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J46">
         <v>4.7</v>
       </c>
       <c r="K46">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -13292,22 +13292,22 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P46">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q46">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="R46">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S46">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="T46">
         <v>1.68</v>
@@ -13370,64 +13370,64 @@
         <v>1000</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO46">
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF46">
         <v>1.01</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -13510,22 +13510,22 @@
         <v>478</v>
       </c>
       <c r="F47">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G47">
         <v>2.42</v>
       </c>
       <c r="H47">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J47">
         <v>4</v>
       </c>
       <c r="K47">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -13534,31 +13534,31 @@
         <v>1.03</v>
       </c>
       <c r="N47">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O47">
         <v>1.15</v>
       </c>
       <c r="P47">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q47">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R47">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S47">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T47">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U47">
         <v>3</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
         <v>1.7</v>
@@ -13567,25 +13567,25 @@
         <v>34</v>
       </c>
       <c r="Y47">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z47">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA47">
         <v>50</v>
       </c>
       <c r="AB47">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC47">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD47">
         <v>16</v>
       </c>
       <c r="AE47">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF47">
         <v>22</v>
@@ -13594,34 +13594,34 @@
         <v>14.5</v>
       </c>
       <c r="AH47">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI47">
         <v>34</v>
       </c>
       <c r="AJ47">
+        <v>65</v>
+      </c>
+      <c r="AK47">
+        <v>23</v>
+      </c>
+      <c r="AL47">
         <v>38</v>
       </c>
-      <c r="AK47">
-        <v>26</v>
-      </c>
-      <c r="AL47">
-        <v>30</v>
-      </c>
       <c r="AM47">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AN47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO47">
         <v>14.5</v>
       </c>
       <c r="AP47">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="AQ47">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR47">
         <v>21</v>
@@ -13630,43 +13630,43 @@
         <v>34</v>
       </c>
       <c r="AT47">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU47">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV47">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW47">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX47">
         <v>17.5</v>
       </c>
       <c r="AY47">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ47">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA47">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BB47">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BC47">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD47">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BE47">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="BF47">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BG47">
         <v>12</v>
@@ -13794,7 +13794,7 @@
         <v>2.78</v>
       </c>
       <c r="T48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U48">
         <v>2.32</v>
@@ -13902,7 +13902,7 @@
         <v>24</v>
       </c>
       <c r="BD48">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE48">
         <v>60</v>
@@ -13997,49 +13997,49 @@
         <v>2.68</v>
       </c>
       <c r="G49">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H49">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I49">
         <v>3</v>
       </c>
       <c r="J49">
+        <v>3.2</v>
+      </c>
+      <c r="K49">
+        <v>3.4</v>
+      </c>
+      <c r="L49">
+        <v>1.01</v>
+      </c>
+      <c r="M49">
+        <v>1.08</v>
+      </c>
+      <c r="N49">
         <v>3.15</v>
       </c>
-      <c r="K49">
-        <v>3.45</v>
-      </c>
-      <c r="L49">
-        <v>1.01</v>
-      </c>
-      <c r="M49">
-        <v>1.07</v>
-      </c>
-      <c r="N49">
-        <v>3.1</v>
-      </c>
       <c r="O49">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P49">
         <v>1.73</v>
       </c>
       <c r="Q49">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S49">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T49">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U49">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V49">
         <v>1.5</v>
@@ -14105,13 +14105,13 @@
         <v>10</v>
       </c>
       <c r="AQ49">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR49">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS49">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT49">
         <v>8.6</v>
@@ -14120,40 +14120,40 @@
         <v>6.6</v>
       </c>
       <c r="AV49">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW49">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX49">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY49">
         <v>11</v>
       </c>
       <c r="AZ49">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA49">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB49">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC49">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD49">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE49">
         <v>5.1</v>
       </c>
       <c r="BF49">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG49">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -14236,7 +14236,7 @@
         <v>481</v>
       </c>
       <c r="F50">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G50">
         <v>2.56</v>
@@ -14245,16 +14245,16 @@
         <v>3.2</v>
       </c>
       <c r="I50">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J50">
         <v>3.15</v>
       </c>
       <c r="K50">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L50">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M50">
         <v>1.08</v>
@@ -14508,7 +14508,7 @@
         <v>1.16</v>
       </c>
       <c r="P51">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q51">
         <v>1.16</v>
@@ -14517,7 +14517,7 @@
         <v>1.18</v>
       </c>
       <c r="S51">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -14526,7 +14526,7 @@
         <v>1.01</v>
       </c>
       <c r="V51">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W51">
         <v>1.32</v>
@@ -14977,7 +14977,7 @@
         <v>3.85</v>
       </c>
       <c r="K53">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L53">
         <v>1.01</v>
@@ -14986,7 +14986,7 @@
         <v>1.04</v>
       </c>
       <c r="N53">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O53">
         <v>1.21</v>
@@ -15001,7 +15001,7 @@
         <v>1.5</v>
       </c>
       <c r="S53">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T53">
         <v>1.58</v>
@@ -15016,7 +15016,7 @@
         <v>1.34</v>
       </c>
       <c r="X53">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y53">
         <v>14</v>
@@ -15073,7 +15073,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ53">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR53">
         <v>12.5</v>
@@ -15118,7 +15118,7 @@
         <v>50</v>
       </c>
       <c r="BF53">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG53">
         <v>9.199999999999999</v>
@@ -15213,16 +15213,16 @@
         <v>1.9</v>
       </c>
       <c r="I54">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J54">
         <v>3.85</v>
       </c>
       <c r="K54">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L54">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M54">
         <v>1.01</v>
@@ -15231,13 +15231,13 @@
         <v>5</v>
       </c>
       <c r="O54">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P54">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q54">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R54">
         <v>1.55</v>
@@ -15252,7 +15252,7 @@
         <v>2.42</v>
       </c>
       <c r="V54">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W54">
         <v>1.31</v>
@@ -15309,7 +15309,7 @@
         <v>36</v>
       </c>
       <c r="AO54">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP54">
         <v>17</v>
@@ -15366,64 +15366,64 @@
         <v>7.2</v>
       </c>
       <c r="BH54">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI54">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ54">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK54">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL54">
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN54">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO54">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP54">
         <v>1000</v>
       </c>
       <c r="BQ54">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR54">
         <v>1000</v>
       </c>
       <c r="BS54">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT54">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU54">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV54">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW54">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX54">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY54">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ54">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA54">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB54" t="s">
         <v>670</v>
@@ -15446,10 +15446,10 @@
         <v>486</v>
       </c>
       <c r="F55">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G55">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H55">
         <v>2.7</v>
@@ -15470,16 +15470,16 @@
         <v>1.01</v>
       </c>
       <c r="N55">
-        <v>2.78</v>
+        <v>5.3</v>
       </c>
       <c r="O55">
         <v>1.12</v>
       </c>
       <c r="P55">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="Q55">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="R55">
         <v>1.63</v>
@@ -15697,13 +15697,13 @@
         <v>4.5</v>
       </c>
       <c r="I56">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J56">
         <v>4.1</v>
       </c>
       <c r="K56">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -15712,22 +15712,22 @@
         <v>1.03</v>
       </c>
       <c r="N56">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O56">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P56">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="Q56">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R56">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S56">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="T56">
         <v>1.46</v>
@@ -15930,28 +15930,28 @@
         <v>488</v>
       </c>
       <c r="F57">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G57">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H57">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I57">
         <v>5.1</v>
       </c>
       <c r="J57">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K57">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L57">
         <v>1.01</v>
       </c>
       <c r="M57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N57">
         <v>4.4</v>
@@ -15981,7 +15981,7 @@
         <v>1.27</v>
       </c>
       <c r="W57">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -16175,7 +16175,7 @@
         <v>2</v>
       </c>
       <c r="G58">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H58">
         <v>3.6</v>
@@ -16196,7 +16196,7 @@
         <v>1.01</v>
       </c>
       <c r="N58">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="O58">
         <v>1.24</v>
@@ -16211,7 +16211,7 @@
         <v>1.41</v>
       </c>
       <c r="S58">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T58">
         <v>1.66</v>
@@ -16417,16 +16417,16 @@
         <v>2.24</v>
       </c>
       <c r="G59">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H59">
         <v>2.88</v>
       </c>
       <c r="I59">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J59">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K59">
         <v>4.7</v>
@@ -16462,10 +16462,10 @@
         <v>1.01</v>
       </c>
       <c r="V59">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W59">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -16656,22 +16656,22 @@
         <v>491</v>
       </c>
       <c r="F60">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="G60">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H60">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I60">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J60">
         <v>5</v>
       </c>
       <c r="K60">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -16680,34 +16680,34 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="O60">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="P60">
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R60">
+        <v>1.73</v>
+      </c>
+      <c r="S60">
         <v>1.84</v>
       </c>
-      <c r="S60">
-        <v>2.04</v>
-      </c>
       <c r="T60">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U60">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V60">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W60">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -16898,10 +16898,10 @@
         <v>492</v>
       </c>
       <c r="F61">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G61">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H61">
         <v>4.8</v>
@@ -16913,7 +16913,7 @@
         <v>4.6</v>
       </c>
       <c r="K61">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L61">
         <v>1.01</v>
@@ -16922,37 +16922,37 @@
         <v>1.01</v>
       </c>
       <c r="N61">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="O61">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P61">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q61">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R61">
         <v>1.75</v>
       </c>
       <c r="S61">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="T61">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U61">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="V61">
         <v>1.21</v>
       </c>
       <c r="W61">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X61">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y61">
         <v>34</v>
@@ -16979,7 +16979,7 @@
         <v>16.5</v>
       </c>
       <c r="AG61">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH61">
         <v>19.5</v>
@@ -17012,25 +17012,25 @@
         <v>4.5</v>
       </c>
       <c r="AR61">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS61">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT61">
         <v>11.5</v>
       </c>
       <c r="AU61">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV61">
         <v>16</v>
       </c>
       <c r="AW61">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX61">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY61">
         <v>9.6</v>
@@ -17039,7 +17039,7 @@
         <v>13</v>
       </c>
       <c r="BA61">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB61">
         <v>13.5</v>
@@ -17051,10 +17051,10 @@
         <v>18</v>
       </c>
       <c r="BE61">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF61">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG61">
         <v>4.6</v>
@@ -17140,7 +17140,7 @@
         <v>493</v>
       </c>
       <c r="F62">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G62">
         <v>1.93</v>
@@ -17149,7 +17149,7 @@
         <v>4.3</v>
       </c>
       <c r="I62">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J62">
         <v>3.9</v>
@@ -17176,10 +17176,10 @@
         <v>1.71</v>
       </c>
       <c r="R62">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S62">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T62">
         <v>1.58</v>
@@ -17227,7 +17227,7 @@
         <v>22</v>
       </c>
       <c r="AI62">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ62">
         <v>25</v>
@@ -17418,10 +17418,10 @@
         <v>1.6</v>
       </c>
       <c r="R63">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S63">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T63">
         <v>1.01</v>
@@ -17448,7 +17448,7 @@
         <v>1000</v>
       </c>
       <c r="AB63">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC63">
         <v>16.5</v>
@@ -17645,25 +17645,25 @@
         <v>1.01</v>
       </c>
       <c r="M64">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N64">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O64">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P64">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q64">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="R64">
         <v>1.52</v>
       </c>
       <c r="S64">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T64">
         <v>1.51</v>
@@ -17678,7 +17678,7 @@
         <v>1.69</v>
       </c>
       <c r="X64">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y64">
         <v>19</v>
@@ -17899,7 +17899,7 @@
         <v>2.2</v>
       </c>
       <c r="Q65">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="R65">
         <v>1.48</v>
@@ -18126,34 +18126,34 @@
         <v>3.75</v>
       </c>
       <c r="L66">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M66">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N66">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O66">
         <v>1.33</v>
       </c>
       <c r="P66">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q66">
         <v>2.04</v>
       </c>
       <c r="R66">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S66">
         <v>3.65</v>
       </c>
       <c r="T66">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="U66">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="V66">
         <v>1.29</v>
@@ -18174,7 +18174,7 @@
         <v>120</v>
       </c>
       <c r="AB66">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC66">
         <v>9.800000000000001</v>
@@ -18210,22 +18210,22 @@
         <v>140</v>
       </c>
       <c r="AN66">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO66">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP66">
         <v>11.5</v>
       </c>
       <c r="AQ66">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR66">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS66">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT66">
         <v>7.8</v>
@@ -18234,10 +18234,10 @@
         <v>7.2</v>
       </c>
       <c r="AV66">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW66">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX66">
         <v>10.5</v>
@@ -18249,25 +18249,25 @@
         <v>16.5</v>
       </c>
       <c r="BA66">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB66">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BC66">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD66">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE66">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF66">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG66">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -18374,28 +18374,28 @@
         <v>1.04</v>
       </c>
       <c r="N67">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O67">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P67">
         <v>2.28</v>
       </c>
       <c r="Q67">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R67">
         <v>1.53</v>
       </c>
       <c r="S67">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T67">
         <v>1.58</v>
       </c>
       <c r="U67">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V67">
         <v>1.49</v>
@@ -18452,7 +18452,7 @@
         <v>85</v>
       </c>
       <c r="AN67">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO67">
         <v>19</v>
@@ -18461,7 +18461,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ67">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR67">
         <v>19.5</v>
@@ -18470,7 +18470,7 @@
         <v>10.5</v>
       </c>
       <c r="AT67">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU67">
         <v>8.199999999999999</v>
@@ -18491,19 +18491,19 @@
         <v>13</v>
       </c>
       <c r="BA67">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB67">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC67">
         <v>20</v>
       </c>
       <c r="BD67">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF67">
         <v>12</v>
@@ -18595,7 +18595,7 @@
         <v>2.18</v>
       </c>
       <c r="G68">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H68">
         <v>3.4</v>
@@ -18628,7 +18628,7 @@
         <v>2.3</v>
       </c>
       <c r="R68">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S68">
         <v>4.2</v>
@@ -18640,10 +18640,10 @@
         <v>1.01</v>
       </c>
       <c r="V68">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W68">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -18837,7 +18837,7 @@
         <v>1.99</v>
       </c>
       <c r="G69">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>4.8</v>
@@ -18852,7 +18852,7 @@
         <v>3.45</v>
       </c>
       <c r="L69">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M69">
         <v>1.09</v>
@@ -18885,7 +18885,7 @@
         <v>1.25</v>
       </c>
       <c r="W69">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X69">
         <v>11.5</v>
@@ -19106,7 +19106,7 @@
         <v>1.02</v>
       </c>
       <c r="P70">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q70">
         <v>1.34</v>
@@ -19318,13 +19318,13 @@
         <v>502</v>
       </c>
       <c r="F71">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G71">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H71">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I71">
         <v>3.55</v>
@@ -19342,37 +19342,37 @@
         <v>1.1</v>
       </c>
       <c r="N71">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="O71">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P71">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q71">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R71">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S71">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T71">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U71">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V71">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W71">
         <v>1.61</v>
       </c>
       <c r="X71">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y71">
         <v>12.5</v>
@@ -19435,10 +19435,10 @@
         <v>17</v>
       </c>
       <c r="AS71">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT71">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU71">
         <v>6.6</v>
@@ -19447,37 +19447,37 @@
         <v>11</v>
       </c>
       <c r="AW71">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX71">
         <v>11.5</v>
       </c>
       <c r="AY71">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ71">
         <v>16.5</v>
       </c>
       <c r="BA71">
+        <v>5.9</v>
+      </c>
+      <c r="BB71">
+        <v>5.8</v>
+      </c>
+      <c r="BC71">
         <v>5.6</v>
       </c>
-      <c r="BB71">
-        <v>5.3</v>
-      </c>
-      <c r="BC71">
-        <v>5.2</v>
-      </c>
       <c r="BD71">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE71">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF71">
         <v>21</v>
       </c>
       <c r="BG71">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -19572,7 +19572,7 @@
         <v>6.4</v>
       </c>
       <c r="J72">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K72">
         <v>6.8</v>
@@ -19587,13 +19587,13 @@
         <v>4</v>
       </c>
       <c r="O72">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P72">
         <v>1.96</v>
       </c>
       <c r="Q72">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="R72">
         <v>1.34</v>
@@ -19802,13 +19802,13 @@
         <v>504</v>
       </c>
       <c r="F73">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G73">
         <v>2.78</v>
       </c>
       <c r="H73">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="I73">
         <v>3.4</v>
@@ -19817,7 +19817,7 @@
         <v>3.35</v>
       </c>
       <c r="K73">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="L73">
         <v>1.33</v>
@@ -19832,10 +19832,10 @@
         <v>1.33</v>
       </c>
       <c r="P73">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R73">
         <v>1.25</v>
@@ -20044,7 +20044,7 @@
         <v>505</v>
       </c>
       <c r="F74">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G74">
         <v>1.38</v>
@@ -20068,13 +20068,13 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O74">
         <v>1.18</v>
       </c>
       <c r="P74">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q74">
         <v>1.55</v>
@@ -20089,7 +20089,7 @@
         <v>1.91</v>
       </c>
       <c r="U74">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V74">
         <v>1.08</v>
@@ -20122,7 +20122,7 @@
         <v>180</v>
       </c>
       <c r="AF74">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG74">
         <v>12.5</v>
@@ -20146,7 +20146,7 @@
         <v>150</v>
       </c>
       <c r="AN74">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO74">
         <v>210</v>
@@ -20528,22 +20528,22 @@
         <v>507</v>
       </c>
       <c r="F76">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="G76">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H76">
         <v>4</v>
       </c>
       <c r="I76">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J76">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K76">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L76">
         <v>1.01</v>
@@ -20558,10 +20558,10 @@
         <v>1.21</v>
       </c>
       <c r="P76">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q76">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R76">
         <v>1.37</v>
@@ -20576,10 +20576,10 @@
         <v>1.01</v>
       </c>
       <c r="V76">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W76">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X76">
         <v>1000</v>
@@ -20770,16 +20770,16 @@
         <v>508</v>
       </c>
       <c r="F77">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G77">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H77">
         <v>3</v>
       </c>
       <c r="I77">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J77">
         <v>3.6</v>
@@ -20803,7 +20803,7 @@
         <v>2.1</v>
       </c>
       <c r="Q77">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="R77">
         <v>1.41</v>
@@ -21021,16 +21021,16 @@
         <v>4</v>
       </c>
       <c r="I78">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K78">
         <v>4.1</v>
       </c>
       <c r="L78">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M78">
         <v>1.04</v>
@@ -21060,7 +21060,7 @@
         <v>2.6</v>
       </c>
       <c r="V78">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W78">
         <v>2</v>
@@ -21090,7 +21090,7 @@
         <v>44</v>
       </c>
       <c r="AF78">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG78">
         <v>10.5</v>
@@ -21278,13 +21278,13 @@
         <v>1.01</v>
       </c>
       <c r="N79">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="O79">
         <v>1.17</v>
       </c>
       <c r="P79">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q79">
         <v>1.59</v>
@@ -21496,19 +21496,19 @@
         <v>511</v>
       </c>
       <c r="F80">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G80">
         <v>1.49</v>
       </c>
       <c r="H80">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I80">
         <v>7.4</v>
       </c>
       <c r="J80">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K80">
         <v>5.4</v>
@@ -21586,7 +21586,7 @@
         <v>65</v>
       </c>
       <c r="AJ80">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK80">
         <v>14</v>
@@ -21652,10 +21652,10 @@
         <v>60</v>
       </c>
       <c r="BF80">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG80">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH80">
         <v>1000</v>
@@ -21756,7 +21756,7 @@
         <v>3.9</v>
       </c>
       <c r="L81">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M81">
         <v>1.05</v>
@@ -21765,7 +21765,7 @@
         <v>5</v>
       </c>
       <c r="O81">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P81">
         <v>2.34</v>
@@ -21843,7 +21843,7 @@
         <v>32</v>
       </c>
       <c r="AO81">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP81">
         <v>17.5</v>
@@ -22052,19 +22052,19 @@
         <v>10.5</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE82">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AF82">
         <v>42</v>
       </c>
       <c r="AG82">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH82">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI82">
         <v>23</v>
@@ -22103,7 +22103,7 @@
         <v>25</v>
       </c>
       <c r="AU82">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV82">
         <v>9.4</v>
@@ -22124,7 +22124,7 @@
         <v>21</v>
       </c>
       <c r="BB82">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BC82">
         <v>38</v>
@@ -22136,64 +22136,64 @@
         <v>44</v>
       </c>
       <c r="BF82">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG82">
         <v>6.6</v>
       </c>
       <c r="BH82">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI82">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ82">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK82">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL82">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM82">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN82">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO82">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP82">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ82">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR82">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS82">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT82">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU82">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV82">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW82">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX82">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY82">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ82">
         <v>0</v>
@@ -22252,7 +22252,7 @@
         <v>1.16</v>
       </c>
       <c r="P83">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q83">
         <v>1.51</v>
@@ -22264,7 +22264,7 @@
         <v>2.28</v>
       </c>
       <c r="T83">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U83">
         <v>2.98</v>
@@ -22282,7 +22282,7 @@
         <v>18</v>
       </c>
       <c r="Z83">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA83">
         <v>34</v>
@@ -22303,13 +22303,13 @@
         <v>26</v>
       </c>
       <c r="AG83">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH83">
         <v>14</v>
       </c>
       <c r="AI83">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ83">
         <v>48</v>
@@ -22345,7 +22345,7 @@
         <v>19.5</v>
       </c>
       <c r="AU83">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV83">
         <v>10.5</v>
@@ -22375,13 +22375,13 @@
         <v>26</v>
       </c>
       <c r="BE83">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF83">
         <v>14</v>
       </c>
       <c r="BG83">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH83">
         <v>1000</v>
@@ -22467,7 +22467,7 @@
         <v>2.28</v>
       </c>
       <c r="G84">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H84">
         <v>3.3</v>
@@ -22485,7 +22485,7 @@
         <v>1.44</v>
       </c>
       <c r="M84">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N84">
         <v>3.15</v>
@@ -22503,7 +22503,7 @@
         <v>1.28</v>
       </c>
       <c r="S84">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T84">
         <v>1.82</v>
@@ -22515,7 +22515,7 @@
         <v>1.34</v>
       </c>
       <c r="W84">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X84">
         <v>13.5</v>
@@ -22524,10 +22524,10 @@
         <v>12.5</v>
       </c>
       <c r="Z84">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA84">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB84">
         <v>11</v>
@@ -22593,7 +22593,7 @@
         <v>11.5</v>
       </c>
       <c r="AW84">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX84">
         <v>11</v>
@@ -22623,7 +22623,7 @@
         <v>17.5</v>
       </c>
       <c r="BG84">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH84">
         <v>3.25</v>
@@ -22641,7 +22641,7 @@
         <v>1000</v>
       </c>
       <c r="BM84">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN84">
         <v>5.2</v>
@@ -22653,7 +22653,7 @@
         <v>18</v>
       </c>
       <c r="BQ84">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR84">
         <v>36</v>
@@ -22671,10 +22671,10 @@
         <v>34</v>
       </c>
       <c r="BW84">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX84">
-        <v>910</v>
+        <v>48</v>
       </c>
       <c r="BY84">
         <v>8.4</v>
@@ -22683,7 +22683,7 @@
         <v>34</v>
       </c>
       <c r="CA84">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB84" t="s">
         <v>670</v>
@@ -22727,7 +22727,7 @@
         <v>1.35</v>
       </c>
       <c r="M85">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N85">
         <v>3.25</v>
@@ -22739,7 +22739,7 @@
         <v>1.82</v>
       </c>
       <c r="Q85">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R85">
         <v>1.29</v>
@@ -22969,19 +22969,19 @@
         <v>1.37</v>
       </c>
       <c r="M86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N86">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="O86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P86">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q86">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="R86">
         <v>1.24</v>
@@ -23193,7 +23193,7 @@
         <v>1.59</v>
       </c>
       <c r="G87">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H87">
         <v>5.9</v>
@@ -23205,31 +23205,31 @@
         <v>3.95</v>
       </c>
       <c r="K87">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L87">
         <v>1.01</v>
       </c>
       <c r="M87">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N87">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="O87">
         <v>1.26</v>
       </c>
       <c r="P87">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q87">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S87">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="T87">
         <v>1.91</v>
@@ -23241,7 +23241,7 @@
         <v>1.15</v>
       </c>
       <c r="W87">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X87">
         <v>18</v>
@@ -23537,7 +23537,7 @@
         <v>5.5</v>
       </c>
       <c r="AO88">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP88">
         <v>20</v>
@@ -23698,22 +23698,22 @@
         <v>1.02</v>
       </c>
       <c r="N89">
-        <v>7.8</v>
+        <v>3.15</v>
       </c>
       <c r="O89">
         <v>1.1</v>
       </c>
       <c r="P89">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q89">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R89">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="S89">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="T89">
         <v>1.36</v>
@@ -23764,7 +23764,7 @@
         <v>25</v>
       </c>
       <c r="AJ89">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK89">
         <v>26</v>
@@ -23925,7 +23925,7 @@
         <v>1.96</v>
       </c>
       <c r="I90">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="J90">
         <v>3.3</v>
@@ -23964,7 +23964,7 @@
         <v>1.01</v>
       </c>
       <c r="V90">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="W90">
         <v>1.27</v>
@@ -24403,7 +24403,7 @@
         <v>3.25</v>
       </c>
       <c r="G92">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H92">
         <v>1.9</v>
@@ -24412,7 +24412,7 @@
         <v>2.12</v>
       </c>
       <c r="J92">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K92">
         <v>6</v>
@@ -24451,7 +24451,7 @@
         <v>1.89</v>
       </c>
       <c r="W92">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X92">
         <v>1000</v>
@@ -24666,10 +24666,10 @@
         <v>1.01</v>
       </c>
       <c r="N93">
+        <v>3.2</v>
+      </c>
+      <c r="O93">
         <v>1.26</v>
-      </c>
-      <c r="O93">
-        <v>1.25</v>
       </c>
       <c r="P93">
         <v>1.26</v>
@@ -24678,10 +24678,10 @@
         <v>1.27</v>
       </c>
       <c r="R93">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S93">
-        <v>2.62</v>
+        <v>1.28</v>
       </c>
       <c r="T93">
         <v>1.01</v>
@@ -24908,16 +24908,16 @@
         <v>1.01</v>
       </c>
       <c r="N94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q94">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R94">
         <v>1.18</v>
@@ -25126,7 +25126,7 @@
         <v>526</v>
       </c>
       <c r="F95">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G95">
         <v>1.3</v>
@@ -25141,7 +25141,7 @@
         <v>7.6</v>
       </c>
       <c r="K95">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L95">
         <v>1.01</v>
@@ -25150,22 +25150,22 @@
         <v>1.01</v>
       </c>
       <c r="N95">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="O95">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P95">
         <v>5.1</v>
       </c>
       <c r="Q95">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R95">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="S95">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T95">
         <v>1.5</v>
@@ -25658,10 +25658,10 @@
         <v>1.01</v>
       </c>
       <c r="V97">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W97">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X97">
         <v>1000</v>
@@ -26339,7 +26339,7 @@
         <v>2.1</v>
       </c>
       <c r="G100">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H100">
         <v>3.35</v>
@@ -26348,10 +26348,10 @@
         <v>3.45</v>
       </c>
       <c r="J100">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K100">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L100">
         <v>1.01</v>
@@ -26360,22 +26360,22 @@
         <v>1.01</v>
       </c>
       <c r="N100">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="O100">
         <v>1.01</v>
       </c>
       <c r="P100">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q100">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R100">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S100">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T100">
         <v>1.01</v>
@@ -26387,7 +26387,7 @@
         <v>1.4</v>
       </c>
       <c r="W100">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X100">
         <v>1000</v>
@@ -26599,25 +26599,25 @@
         <v>1.01</v>
       </c>
       <c r="M101">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N101">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O101">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P101">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q101">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R101">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S101">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="T101">
         <v>1.67</v>
@@ -26635,109 +26635,109 @@
         <v>1000</v>
       </c>
       <c r="Y101">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z101">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA101">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB101">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC101">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD101">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE101">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF101">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG101">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH101">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI101">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ101">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK101">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL101">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM101">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN101">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO101">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP101">
         <v>1.01</v>
       </c>
       <c r="AQ101">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU101">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV101">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF101">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG101">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH101">
         <v>1000</v>
@@ -26829,7 +26829,7 @@
         <v>2.16</v>
       </c>
       <c r="I102">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="J102">
         <v>2.78</v>
@@ -26868,7 +26868,7 @@
         <v>1.01</v>
       </c>
       <c r="V102">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W102">
         <v>1.33</v>
@@ -27579,19 +27579,19 @@
         <v>2.14</v>
       </c>
       <c r="Q105">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R105">
         <v>1.45</v>
       </c>
       <c r="S105">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T105">
         <v>1.55</v>
       </c>
       <c r="U105">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V105">
         <v>1.32</v>
@@ -27803,7 +27803,7 @@
         <v>4</v>
       </c>
       <c r="K106">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L106">
         <v>1.28</v>
@@ -27827,7 +27827,7 @@
         <v>1.5</v>
       </c>
       <c r="S106">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T106">
         <v>1.69</v>
@@ -27944,7 +27944,7 @@
         <v>5</v>
       </c>
       <c r="BF106">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG106">
         <v>4.9</v>
@@ -28030,7 +28030,7 @@
         <v>538</v>
       </c>
       <c r="F107">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G107">
         <v>1.56</v>
@@ -28045,7 +28045,7 @@
         <v>4.7</v>
       </c>
       <c r="K107">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L107">
         <v>1.31</v>
@@ -28090,10 +28090,10 @@
         <v>32</v>
       </c>
       <c r="Z107">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA107">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AB107">
         <v>12</v>
@@ -28120,7 +28120,7 @@
         <v>80</v>
       </c>
       <c r="AJ107">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK107">
         <v>15</v>
@@ -28135,7 +28135,7 @@
         <v>6.4</v>
       </c>
       <c r="AO107">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP107">
         <v>20</v>
@@ -28159,19 +28159,19 @@
         <v>23</v>
       </c>
       <c r="AW107">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX107">
         <v>9.199999999999999</v>
       </c>
       <c r="AY107">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ107">
         <v>18.5</v>
       </c>
       <c r="BA107">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB107">
         <v>12.5</v>
@@ -28180,7 +28180,7 @@
         <v>13.5</v>
       </c>
       <c r="BD107">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE107">
         <v>12.5</v>
@@ -28284,7 +28284,7 @@
         <v>3.3</v>
       </c>
       <c r="J108">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K108">
         <v>3.6</v>
@@ -28299,25 +28299,25 @@
         <v>2.82</v>
       </c>
       <c r="O108">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P108">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="Q108">
         <v>2.08</v>
       </c>
       <c r="R108">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S108">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T108">
         <v>1.72</v>
       </c>
       <c r="U108">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V108">
         <v>1.43</v>
@@ -28347,7 +28347,7 @@
         <v>16.5</v>
       </c>
       <c r="AE108">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF108">
         <v>18</v>
@@ -28377,7 +28377,7 @@
         <v>28</v>
       </c>
       <c r="AO108">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP108">
         <v>11</v>
@@ -28410,7 +28410,7 @@
         <v>10</v>
       </c>
       <c r="AZ108">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA108">
         <v>5.2</v>
@@ -28759,10 +28759,10 @@
         <v>2.32</v>
       </c>
       <c r="G110">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="H110">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="I110">
         <v>3.15</v>
@@ -28771,31 +28771,31 @@
         <v>3.6</v>
       </c>
       <c r="K110">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L110">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M110">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N110">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O110">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P110">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q110">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R110">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S110">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="T110">
         <v>1.53</v>
@@ -28807,7 +28807,7 @@
         <v>1.46</v>
       </c>
       <c r="W110">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="X110">
         <v>23</v>
@@ -28963,7 +28963,7 @@
         <v>26</v>
       </c>
       <c r="BW110">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX110">
         <v>38</v>
@@ -29267,25 +29267,25 @@
         <v>11</v>
       </c>
       <c r="O112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P112">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q112">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="R112">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="S112">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="T112">
         <v>1.42</v>
       </c>
       <c r="U112">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V112">
         <v>1.14</v>
@@ -29497,7 +29497,7 @@
         <v>3.75</v>
       </c>
       <c r="K113">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L113">
         <v>1.01</v>
@@ -29629,7 +29629,7 @@
         <v>21</v>
       </c>
       <c r="BC113">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD113">
         <v>27</v>
@@ -29748,16 +29748,16 @@
         <v>1.07</v>
       </c>
       <c r="N114">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="O114">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P114">
         <v>1.96</v>
       </c>
       <c r="Q114">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R114">
         <v>1.37</v>
@@ -29999,13 +29999,13 @@
         <v>2.28</v>
       </c>
       <c r="Q115">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R115">
         <v>1.51</v>
       </c>
       <c r="S115">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T115">
         <v>1.56</v>
@@ -30059,7 +30059,7 @@
         <v>40</v>
       </c>
       <c r="AK115">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL115">
         <v>38</v>
@@ -30068,7 +30068,7 @@
         <v>75</v>
       </c>
       <c r="AN115">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO115">
         <v>25</v>
@@ -30208,7 +30208,7 @@
         <v>547</v>
       </c>
       <c r="F116">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="G116">
         <v>2.76</v>
@@ -30217,13 +30217,13 @@
         <v>2.66</v>
       </c>
       <c r="I116">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J116">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K116">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="L116">
         <v>1.01</v>
@@ -30232,16 +30232,16 @@
         <v>1.01</v>
       </c>
       <c r="N116">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O116">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P116">
         <v>1.94</v>
       </c>
       <c r="Q116">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R116">
         <v>1.31</v>
@@ -30256,10 +30256,10 @@
         <v>1.01</v>
       </c>
       <c r="V116">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W116">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X116">
         <v>1000</v>
@@ -30453,7 +30453,7 @@
         <v>2.52</v>
       </c>
       <c r="G117">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H117">
         <v>2.6</v>
@@ -30468,7 +30468,7 @@
         <v>4.6</v>
       </c>
       <c r="L117">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M117">
         <v>1.04</v>
@@ -30483,7 +30483,7 @@
         <v>2.4</v>
       </c>
       <c r="Q117">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R117">
         <v>1.55</v>
@@ -30701,16 +30701,16 @@
         <v>3.05</v>
       </c>
       <c r="I118">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J118">
         <v>3.7</v>
       </c>
       <c r="K118">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L118">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M118">
         <v>1.04</v>
@@ -30722,25 +30722,25 @@
         <v>1.2</v>
       </c>
       <c r="P118">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q118">
         <v>1.62</v>
       </c>
       <c r="R118">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S118">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T118">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U118">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W118">
         <v>1.72</v>
@@ -30854,13 +30854,13 @@
         <v>17.5</v>
       </c>
       <c r="BH118">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI118">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ118">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK118">
         <v>1.01</v>
@@ -30872,43 +30872,43 @@
         <v>1.01</v>
       </c>
       <c r="BN118">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO118">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP118">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ118">
         <v>1.01</v>
       </c>
       <c r="BR118">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS118">
         <v>1.01</v>
       </c>
       <c r="BT118">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU118">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV118">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW118">
         <v>1.01</v>
       </c>
       <c r="BX118">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY118">
         <v>1.01</v>
       </c>
       <c r="BZ118">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA118">
         <v>1.01</v>
@@ -30934,7 +30934,7 @@
         <v>550</v>
       </c>
       <c r="F119">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G119">
         <v>2.48</v>
@@ -30943,22 +30943,22 @@
         <v>3.05</v>
       </c>
       <c r="I119">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J119">
         <v>3.55</v>
       </c>
       <c r="K119">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L119">
         <v>1.01</v>
       </c>
       <c r="M119">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N119">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="O119">
         <v>1.24</v>
@@ -30967,13 +30967,13 @@
         <v>2.14</v>
       </c>
       <c r="Q119">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R119">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S119">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T119">
         <v>1.61</v>
@@ -30985,7 +30985,7 @@
         <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X119">
         <v>20</v>
@@ -31179,16 +31179,16 @@
         <v>1.76</v>
       </c>
       <c r="G120">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H120">
         <v>3.8</v>
       </c>
       <c r="I120">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J120">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K120">
         <v>6</v>
@@ -31224,10 +31224,10 @@
         <v>1.01</v>
       </c>
       <c r="V120">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W120">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="X120">
         <v>1000</v>
@@ -31427,43 +31427,43 @@
         <v>3.2</v>
       </c>
       <c r="I121">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J121">
         <v>3.5</v>
       </c>
       <c r="K121">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L121">
         <v>1.01</v>
       </c>
       <c r="M121">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N121">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O121">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P121">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Q121">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S121">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T121">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U121">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="V121">
         <v>1.4</v>
@@ -31666,7 +31666,7 @@
         <v>2.06</v>
       </c>
       <c r="H122">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I122">
         <v>4.2</v>
@@ -31771,7 +31771,7 @@
         <v>14</v>
       </c>
       <c r="AQ122">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR122">
         <v>26</v>
@@ -31792,7 +31792,7 @@
         <v>42</v>
       </c>
       <c r="AX122">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY122">
         <v>9.800000000000001</v>
@@ -31801,7 +31801,7 @@
         <v>16</v>
       </c>
       <c r="BA122">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB122">
         <v>22</v>
@@ -31941,7 +31941,7 @@
         <v>1.39</v>
       </c>
       <c r="S123">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T123">
         <v>1.75</v>
@@ -32043,7 +32043,7 @@
         <v>15.5</v>
       </c>
       <c r="BA123">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB123">
         <v>29</v>
@@ -32144,7 +32144,7 @@
         <v>555</v>
       </c>
       <c r="F124">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G124">
         <v>1.7</v>
@@ -32249,7 +32249,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO124">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP124">
         <v>14</v>
@@ -32264,7 +32264,7 @@
         <v>44</v>
       </c>
       <c r="AT124">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU124">
         <v>8.6</v>
@@ -32303,7 +32303,7 @@
         <v>9</v>
       </c>
       <c r="BG124">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH124">
         <v>3.55</v>
@@ -32404,7 +32404,7 @@
         <v>3.6</v>
       </c>
       <c r="L125">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M125">
         <v>1.07</v>
@@ -32539,7 +32539,7 @@
         <v>34</v>
       </c>
       <c r="BE125">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF125">
         <v>19</v>
@@ -32748,13 +32748,13 @@
         <v>150</v>
       </c>
       <c r="AT126">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU126">
         <v>18.5</v>
       </c>
       <c r="AV126">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW126">
         <v>95</v>
@@ -32894,13 +32894,13 @@
         <v>1.01</v>
       </c>
       <c r="N127">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="O127">
         <v>1.23</v>
       </c>
       <c r="P127">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q127">
         <v>1.57</v>
@@ -33145,7 +33145,7 @@
         <v>2.22</v>
       </c>
       <c r="Q128">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R128">
         <v>1.46</v>
@@ -33244,7 +33244,7 @@
         <v>26</v>
       </c>
       <c r="AX128">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY128">
         <v>10.5</v>
@@ -33360,7 +33360,7 @@
         <v>2.84</v>
       </c>
       <c r="H129">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I129">
         <v>2.92</v>
@@ -33372,13 +33372,13 @@
         <v>3.45</v>
       </c>
       <c r="L129">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M129">
         <v>1.09</v>
       </c>
       <c r="N129">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O129">
         <v>1.39</v>
@@ -33408,7 +33408,7 @@
         <v>1.54</v>
       </c>
       <c r="X129">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y129">
         <v>11</v>
@@ -33447,7 +33447,7 @@
         <v>46</v>
       </c>
       <c r="AK129">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL129">
         <v>60</v>
@@ -33495,7 +33495,7 @@
         <v>16.5</v>
       </c>
       <c r="BA129">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB129">
         <v>40</v>
@@ -33507,7 +33507,7 @@
         <v>40</v>
       </c>
       <c r="BE129">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF129">
         <v>24</v>
@@ -33596,7 +33596,7 @@
         <v>561</v>
       </c>
       <c r="F130">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G130">
         <v>1.78</v>
@@ -33608,7 +33608,7 @@
         <v>5.3</v>
       </c>
       <c r="J130">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K130">
         <v>4.4</v>
@@ -33623,13 +33623,13 @@
         <v>2.42</v>
       </c>
       <c r="O130">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P130">
         <v>2.42</v>
       </c>
       <c r="Q130">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="R130">
         <v>1.45</v>
@@ -33734,7 +33734,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ130">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA130">
         <v>36</v>
@@ -33859,7 +33859,7 @@
         <v>1.01</v>
       </c>
       <c r="M131">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N131">
         <v>4.1</v>
@@ -33868,16 +33868,16 @@
         <v>1.26</v>
       </c>
       <c r="P131">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q131">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R131">
         <v>1.41</v>
       </c>
       <c r="S131">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T131">
         <v>1.64</v>
@@ -34101,10 +34101,10 @@
         <v>1.32</v>
       </c>
       <c r="M132">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N132">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O132">
         <v>1.28</v>
@@ -34179,7 +34179,7 @@
         <v>36</v>
       </c>
       <c r="AM132">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN132">
         <v>10.5</v>
@@ -34346,10 +34346,10 @@
         <v>1.06</v>
       </c>
       <c r="N133">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O133">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P133">
         <v>2.08</v>
@@ -34418,7 +34418,7 @@
         <v>19.5</v>
       </c>
       <c r="AL133">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM133">
         <v>120</v>
@@ -34439,7 +34439,7 @@
         <v>38</v>
       </c>
       <c r="AS133">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT133">
         <v>8.199999999999999</v>
@@ -34463,7 +34463,7 @@
         <v>18</v>
       </c>
       <c r="BA133">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB133">
         <v>16</v>
@@ -34475,7 +34475,7 @@
         <v>30</v>
       </c>
       <c r="BE133">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF133">
         <v>9</v>
@@ -34567,7 +34567,7 @@
         <v>2.14</v>
       </c>
       <c r="G134">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H134">
         <v>3.45</v>
@@ -34600,7 +34600,7 @@
         <v>1.96</v>
       </c>
       <c r="R134">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S134">
         <v>3.5</v>
@@ -34615,112 +34615,112 @@
         <v>1.35</v>
       </c>
       <c r="W134">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X134">
+        <v>14.5</v>
+      </c>
+      <c r="Y134">
+        <v>14</v>
+      </c>
+      <c r="Z134">
+        <v>30</v>
+      </c>
+      <c r="AA134">
+        <v>75</v>
+      </c>
+      <c r="AB134">
+        <v>10</v>
+      </c>
+      <c r="AC134">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD134">
         <v>16</v>
-      </c>
-      <c r="Y134">
-        <v>16</v>
-      </c>
-      <c r="Z134">
-        <v>29</v>
-      </c>
-      <c r="AA134">
-        <v>85</v>
-      </c>
-      <c r="AB134">
-        <v>12</v>
-      </c>
-      <c r="AC134">
-        <v>9.4</v>
-      </c>
-      <c r="AD134">
-        <v>18</v>
       </c>
       <c r="AE134">
         <v>48</v>
       </c>
       <c r="AF134">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG134">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH134">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI134">
         <v>60</v>
       </c>
       <c r="AJ134">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK134">
         <v>28</v>
       </c>
       <c r="AL134">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM134">
         <v>120</v>
       </c>
       <c r="AN134">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO134">
         <v>50</v>
       </c>
       <c r="AP134">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ134">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR134">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS134">
-        <v>4.7</v>
+        <v>55</v>
       </c>
       <c r="AT134">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU134">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV134">
+        <v>13.5</v>
+      </c>
+      <c r="AW134">
+        <v>38</v>
+      </c>
+      <c r="AX134">
         <v>12</v>
       </c>
-      <c r="AW134">
-        <v>32</v>
-      </c>
-      <c r="AX134">
-        <v>10.5</v>
-      </c>
       <c r="AY134">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ134">
         <v>15.5</v>
       </c>
       <c r="BA134">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB134">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC134">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD134">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE134">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BF134">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG134">
         <v>29</v>
@@ -34845,10 +34845,10 @@
         <v>1.46</v>
       </c>
       <c r="S135">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T135">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U135">
         <v>2.38</v>
@@ -35072,7 +35072,7 @@
         <v>1.05</v>
       </c>
       <c r="N136">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O136">
         <v>1.25</v>
@@ -35081,25 +35081,25 @@
         <v>2.28</v>
       </c>
       <c r="Q136">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R136">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S136">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T136">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U136">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V136">
         <v>1.12</v>
       </c>
       <c r="W136">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X136">
         <v>20</v>
@@ -35108,7 +35108,7 @@
         <v>29</v>
       </c>
       <c r="Z136">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA136">
         <v>320</v>
@@ -35123,7 +35123,7 @@
         <v>34</v>
       </c>
       <c r="AE136">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF136">
         <v>8.6</v>
@@ -35431,7 +35431,7 @@
         <v>17</v>
       </c>
       <c r="BA137">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB137">
         <v>19.5</v>
@@ -35532,22 +35532,22 @@
         <v>569</v>
       </c>
       <c r="F138">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G138">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H138">
         <v>4.5</v>
       </c>
       <c r="I138">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J138">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K138">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L138">
         <v>1.01</v>
@@ -35562,7 +35562,7 @@
         <v>1.37</v>
       </c>
       <c r="P138">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q138">
         <v>2.12</v>
@@ -35577,37 +35577,37 @@
         <v>1.94</v>
       </c>
       <c r="U138">
+        <v>1.99</v>
+      </c>
+      <c r="V138">
+        <v>1.27</v>
+      </c>
+      <c r="W138">
         <v>2</v>
-      </c>
-      <c r="V138">
-        <v>1.28</v>
-      </c>
-      <c r="W138">
-        <v>1.98</v>
       </c>
       <c r="X138">
         <v>12.5</v>
       </c>
       <c r="Y138">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z138">
         <v>34</v>
       </c>
       <c r="AA138">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB138">
         <v>8.800000000000001</v>
       </c>
       <c r="AC138">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD138">
         <v>18.5</v>
       </c>
       <c r="AE138">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF138">
         <v>11.5</v>
@@ -35637,7 +35637,7 @@
         <v>15.5</v>
       </c>
       <c r="AO138">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP138">
         <v>11</v>
@@ -35661,13 +35661,13 @@
         <v>16</v>
       </c>
       <c r="AW138">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AX138">
         <v>10.5</v>
       </c>
       <c r="AY138">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ138">
         <v>17.5</v>
@@ -35685,13 +35685,13 @@
         <v>36</v>
       </c>
       <c r="BE138">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF138">
         <v>14</v>
       </c>
       <c r="BG138">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BH138">
         <v>1000</v>
@@ -35774,16 +35774,16 @@
         <v>570</v>
       </c>
       <c r="F139">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G139">
         <v>2.02</v>
       </c>
       <c r="H139">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I139">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J139">
         <v>3.75</v>
@@ -35849,7 +35849,7 @@
         <v>18</v>
       </c>
       <c r="AE139">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AF139">
         <v>12.5</v>
@@ -35873,13 +35873,13 @@
         <v>36</v>
       </c>
       <c r="AM139">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN139">
         <v>13</v>
       </c>
       <c r="AO139">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="AP139">
         <v>14</v>
@@ -35894,7 +35894,7 @@
         <v>36</v>
       </c>
       <c r="AT139">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU139">
         <v>7.8</v>
@@ -36267,7 +36267,7 @@
         <v>2.84</v>
       </c>
       <c r="I141">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J141">
         <v>3.6</v>
@@ -36503,13 +36503,13 @@
         <v>3.3</v>
       </c>
       <c r="G142">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H142">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I142">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J142">
         <v>3.5</v>
@@ -36542,19 +36542,19 @@
         <v>3.45</v>
       </c>
       <c r="T142">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U142">
         <v>2.24</v>
       </c>
       <c r="V142">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W142">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X142">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y142">
         <v>10.5</v>
@@ -36617,7 +36617,7 @@
         <v>13.5</v>
       </c>
       <c r="AS142">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT142">
         <v>12.5</v>
@@ -36662,64 +36662,64 @@
         <v>17</v>
       </c>
       <c r="BH142">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI142">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="BJ142">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK142">
-        <v>8.199999999999999</v>
+        <v>2.26</v>
       </c>
       <c r="BL142">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM142">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="BN142">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO142">
-        <v>5.8</v>
+        <v>1.98</v>
       </c>
       <c r="BP142">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ142">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="BR142">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS142">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="BT142">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BU142">
-        <v>4.8</v>
+        <v>1.82</v>
       </c>
       <c r="BV142">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW142">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BX142">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY142">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="BZ142">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA142">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="CB142" t="s">
         <v>670</v>
@@ -36769,13 +36769,13 @@
         <v>3.35</v>
       </c>
       <c r="O143">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P143">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q143">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="R143">
         <v>1.31</v>
@@ -37734,19 +37734,19 @@
         <v>1.09</v>
       </c>
       <c r="N147">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O147">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P147">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="Q147">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R147">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S147">
         <v>4</v>
@@ -37979,7 +37979,7 @@
         <v>7.6</v>
       </c>
       <c r="O148">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P148">
         <v>3.3</v>
@@ -38194,7 +38194,7 @@
         <v>580</v>
       </c>
       <c r="F149">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G149">
         <v>2.46</v>
@@ -38466,10 +38466,10 @@
         <v>1.14</v>
       </c>
       <c r="P150">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q150">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R150">
         <v>1.61</v>
@@ -38708,10 +38708,10 @@
         <v>1.22</v>
       </c>
       <c r="P151">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q151">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R151">
         <v>1.51</v>
@@ -39431,7 +39431,7 @@
         <v>3.25</v>
       </c>
       <c r="O154">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P154">
         <v>1.76</v>
@@ -39443,7 +39443,7 @@
         <v>1.25</v>
       </c>
       <c r="S154">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T154">
         <v>1.01</v>
@@ -39452,7 +39452,7 @@
         <v>1.97</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W154">
         <v>1.66</v>
@@ -39679,13 +39679,13 @@
         <v>2.44</v>
       </c>
       <c r="Q155">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="R155">
         <v>1.59</v>
       </c>
       <c r="S155">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="T155">
         <v>1.01</v>
@@ -40402,10 +40402,10 @@
         <v>1.23</v>
       </c>
       <c r="P158">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q158">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R158">
         <v>1.44</v>
@@ -40653,7 +40653,7 @@
         <v>1.41</v>
       </c>
       <c r="S159">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T159">
         <v>1.01</v>
@@ -40662,7 +40662,7 @@
         <v>1.01</v>
       </c>
       <c r="V159">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W159">
         <v>1.6</v>
@@ -41101,7 +41101,7 @@
         <v>1.98</v>
       </c>
       <c r="G161">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H161">
         <v>3.2</v>
@@ -41122,7 +41122,7 @@
         <v>1.01</v>
       </c>
       <c r="N161">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O161">
         <v>1.34</v>
@@ -41131,13 +41131,13 @@
         <v>1.67</v>
       </c>
       <c r="Q161">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="R161">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="S161">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="T161">
         <v>1.01</v>
@@ -41149,7 +41149,7 @@
         <v>1.26</v>
       </c>
       <c r="W161">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X161">
         <v>1000</v>
@@ -41370,13 +41370,13 @@
         <v>1.14</v>
       </c>
       <c r="P162">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q162">
         <v>1.49</v>
       </c>
       <c r="R162">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S162">
         <v>2.02</v>
@@ -41594,7 +41594,7 @@
         <v>4.3</v>
       </c>
       <c r="J163">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K163">
         <v>4.5</v>
@@ -41606,19 +41606,19 @@
         <v>1.01</v>
       </c>
       <c r="N163">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="O163">
         <v>1.18</v>
       </c>
       <c r="P163">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="Q163">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="R163">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S163">
         <v>2.2</v>
@@ -41851,7 +41851,7 @@
         <v>2.6</v>
       </c>
       <c r="O164">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P164">
         <v>2.6</v>
@@ -42096,10 +42096,10 @@
         <v>1.27</v>
       </c>
       <c r="P165">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q165">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R165">
         <v>1.37</v>
@@ -42574,22 +42574,22 @@
         <v>1.01</v>
       </c>
       <c r="N167">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="O167">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P167">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q167">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R167">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="S167">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="T167">
         <v>1.54</v>
@@ -43037,7 +43037,7 @@
         <v>2.44</v>
       </c>
       <c r="G169">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H169">
         <v>2.58</v>
@@ -43046,7 +43046,7 @@
         <v>2.98</v>
       </c>
       <c r="J169">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K169">
         <v>4.2</v>
@@ -43085,7 +43085,7 @@
         <v>1.5</v>
       </c>
       <c r="W169">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X169">
         <v>1000</v>
@@ -43291,7 +43291,7 @@
         <v>3.95</v>
       </c>
       <c r="K170">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L170">
         <v>1.01</v>
@@ -43306,10 +43306,10 @@
         <v>1.26</v>
       </c>
       <c r="P170">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q170">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R170">
         <v>1.31</v>
@@ -43766,13 +43766,13 @@
         <v>1.69</v>
       </c>
       <c r="H172">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I172">
         <v>6.4</v>
       </c>
       <c r="J172">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K172">
         <v>4.1</v>
@@ -44005,16 +44005,16 @@
         <v>5.2</v>
       </c>
       <c r="G173">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H173">
         <v>1.43</v>
       </c>
       <c r="I173">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J173">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K173">
         <v>220</v>
@@ -44026,16 +44026,16 @@
         <v>1.01</v>
       </c>
       <c r="N173">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O173">
         <v>1.19</v>
       </c>
       <c r="P173">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="Q173">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R173">
         <v>1.45</v>
@@ -44050,10 +44050,10 @@
         <v>1.01</v>
       </c>
       <c r="V173">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X173">
         <v>1000</v>
@@ -44283,7 +44283,7 @@
         <v>1.65</v>
       </c>
       <c r="S174">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="T174">
         <v>1.47</v>
@@ -44516,10 +44516,10 @@
         <v>1.26</v>
       </c>
       <c r="P175">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q175">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R175">
         <v>1.33</v>
@@ -44764,7 +44764,7 @@
         <v>1.55</v>
       </c>
       <c r="R176">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S176">
         <v>2.4</v>
@@ -45006,7 +45006,7 @@
         <v>1.62</v>
       </c>
       <c r="R177">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S177">
         <v>1.64</v>
@@ -45245,7 +45245,7 @@
         <v>1.25</v>
       </c>
       <c r="Q178">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -45454,7 +45454,7 @@
         <v>610</v>
       </c>
       <c r="F179">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G179">
         <v>1.77</v>
@@ -45502,7 +45502,7 @@
         <v>1.01</v>
       </c>
       <c r="V179">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W179">
         <v>2.28</v>
@@ -45735,7 +45735,7 @@
         <v>1.4</v>
       </c>
       <c r="S180">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T180">
         <v>1.82</v>
@@ -45840,7 +45840,7 @@
         <v>30</v>
       </c>
       <c r="BB180">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BC180">
         <v>46</v>
@@ -45849,10 +45849,10 @@
         <v>50</v>
       </c>
       <c r="BE180">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF180">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BG180">
         <v>12</v>
@@ -45968,7 +45968,7 @@
         <v>1.08</v>
       </c>
       <c r="P181">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q181">
         <v>1.26</v>
@@ -45977,10 +45977,10 @@
         <v>2.46</v>
       </c>
       <c r="S181">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T181">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U181">
         <v>2.26</v>
@@ -46004,7 +46004,7 @@
         <v>11.5</v>
       </c>
       <c r="AB181">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AC181">
         <v>25</v>
@@ -46082,7 +46082,7 @@
         <v>23</v>
       </c>
       <c r="BB181">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BC181">
         <v>48</v>
@@ -46210,16 +46210,16 @@
         <v>1.07</v>
       </c>
       <c r="P182">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q182">
         <v>1.07</v>
       </c>
       <c r="R182">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S182">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="T182">
         <v>1.01</v>
@@ -46464,7 +46464,7 @@
         <v>3.2</v>
       </c>
       <c r="T183">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U183">
         <v>2.34</v>
@@ -46599,7 +46599,7 @@
         <v>1000</v>
       </c>
       <c r="BM183">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BN183">
         <v>1000</v>
@@ -46617,31 +46617,31 @@
         <v>1000</v>
       </c>
       <c r="BS183">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BT183">
         <v>1000</v>
       </c>
       <c r="BU183">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="BV183">
         <v>1000</v>
       </c>
       <c r="BW183">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BX183">
         <v>1000</v>
       </c>
       <c r="BY183">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BZ183">
         <v>1000</v>
       </c>
       <c r="CA183">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="CB183" t="s">
         <v>670</v>
@@ -46694,13 +46694,13 @@
         <v>1.27</v>
       </c>
       <c r="P184">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q184">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R184">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S184">
         <v>3</v>
@@ -47178,7 +47178,7 @@
         <v>1.01</v>
       </c>
       <c r="P186">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q186">
         <v>1.89</v>
@@ -47632,16 +47632,16 @@
         <v>619</v>
       </c>
       <c r="F188">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G188">
         <v>2.18</v>
       </c>
       <c r="H188">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I188">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J188">
         <v>4</v>
@@ -47656,16 +47656,16 @@
         <v>1.03</v>
       </c>
       <c r="N188">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O188">
         <v>1.17</v>
       </c>
       <c r="P188">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q188">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="R188">
         <v>1.53</v>
@@ -47785,7 +47785,7 @@
         <v>23</v>
       </c>
       <c r="BE188">
-        <v>44</v>
+        <v>5.9</v>
       </c>
       <c r="BF188">
         <v>8.6</v>
@@ -47883,10 +47883,10 @@
         <v>3.55</v>
       </c>
       <c r="I189">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J189">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K189">
         <v>4.4</v>
@@ -47901,7 +47901,7 @@
         <v>2.96</v>
       </c>
       <c r="O189">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P189">
         <v>1.7</v>
@@ -48119,16 +48119,16 @@
         <v>5</v>
       </c>
       <c r="G190">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H190">
         <v>1.83</v>
       </c>
       <c r="I190">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J190">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K190">
         <v>3.85</v>
@@ -48137,7 +48137,7 @@
         <v>1.01</v>
       </c>
       <c r="M190">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N190">
         <v>3.2</v>
@@ -48146,10 +48146,10 @@
         <v>1.33</v>
       </c>
       <c r="P190">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q190">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R190">
         <v>1.25</v>
@@ -48164,10 +48164,10 @@
         <v>1.01</v>
       </c>
       <c r="V190">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W190">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X190">
         <v>1000</v>
@@ -48212,7 +48212,7 @@
         <v>100</v>
       </c>
       <c r="AL190">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM190">
         <v>1000</v>
@@ -48224,55 +48224,55 @@
         <v>18.5</v>
       </c>
       <c r="AP190">
+        <v>2.62</v>
+      </c>
+      <c r="AQ190">
+        <v>2.1</v>
+      </c>
+      <c r="AR190">
+        <v>2.22</v>
+      </c>
+      <c r="AS190">
+        <v>2.38</v>
+      </c>
+      <c r="AT190">
+        <v>2.34</v>
+      </c>
+      <c r="AU190">
+        <v>2.12</v>
+      </c>
+      <c r="AV190">
+        <v>2.22</v>
+      </c>
+      <c r="AW190">
+        <v>2.4</v>
+      </c>
+      <c r="AX190">
+        <v>2.5</v>
+      </c>
+      <c r="AY190">
+        <v>2.4</v>
+      </c>
+      <c r="AZ190">
+        <v>2.42</v>
+      </c>
+      <c r="BA190">
+        <v>2.5</v>
+      </c>
+      <c r="BB190">
+        <v>2.62</v>
+      </c>
+      <c r="BC190">
         <v>2.56</v>
-      </c>
-      <c r="AQ190">
-        <v>2.06</v>
-      </c>
-      <c r="AR190">
-        <v>2.18</v>
-      </c>
-      <c r="AS190">
-        <v>2.32</v>
-      </c>
-      <c r="AT190">
-        <v>2.3</v>
-      </c>
-      <c r="AU190">
-        <v>2.08</v>
-      </c>
-      <c r="AV190">
-        <v>2.18</v>
-      </c>
-      <c r="AW190">
-        <v>2.34</v>
-      </c>
-      <c r="AX190">
-        <v>2.44</v>
-      </c>
-      <c r="AY190">
-        <v>2.34</v>
-      </c>
-      <c r="AZ190">
-        <v>2.36</v>
-      </c>
-      <c r="BA190">
-        <v>2.44</v>
-      </c>
-      <c r="BB190">
-        <v>2.56</v>
-      </c>
-      <c r="BC190">
-        <v>2.5</v>
       </c>
       <c r="BD190">
         <v>2.56</v>
       </c>
       <c r="BE190">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BF190">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BG190">
         <v>9.199999999999999</v>
@@ -48361,7 +48361,7 @@
         <v>12</v>
       </c>
       <c r="G191">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="H191">
         <v>1.27</v>
@@ -48382,7 +48382,7 @@
         <v>1.03</v>
       </c>
       <c r="N191">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="O191">
         <v>1.18</v>
@@ -48394,7 +48394,7 @@
         <v>1.53</v>
       </c>
       <c r="R191">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S191">
         <v>2.36</v>
@@ -48615,7 +48615,7 @@
         <v>3.7</v>
       </c>
       <c r="K192">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L192">
         <v>1.01</v>
@@ -49087,7 +49087,7 @@
         <v>1.85</v>
       </c>
       <c r="G194">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H194">
         <v>4.1</v>
@@ -49117,7 +49117,7 @@
         <v>2.18</v>
       </c>
       <c r="Q194">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="R194">
         <v>1.37</v>
@@ -49326,7 +49326,7 @@
         <v>626</v>
       </c>
       <c r="F195">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G195">
         <v>3</v>
@@ -49338,10 +49338,10 @@
         <v>3.6</v>
       </c>
       <c r="J195">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K195">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L195">
         <v>0</v>
@@ -49592,16 +49592,16 @@
         <v>1.01</v>
       </c>
       <c r="N196">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O196">
         <v>1.17</v>
       </c>
       <c r="P196">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q196">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R196">
         <v>1.56</v>
@@ -49843,7 +49843,7 @@
         <v>1.74</v>
       </c>
       <c r="Q197">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R197">
         <v>1.2</v>
@@ -50545,7 +50545,7 @@
         <v>1.71</v>
       </c>
       <c r="I200">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J200">
         <v>3.5</v>
@@ -50560,16 +50560,16 @@
         <v>1.1</v>
       </c>
       <c r="N200">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="O200">
         <v>1.32</v>
       </c>
       <c r="P200">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Q200">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="R200">
         <v>1.16</v>
@@ -50584,7 +50584,7 @@
         <v>1.01</v>
       </c>
       <c r="V200">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W200">
         <v>1.17</v>
@@ -50808,13 +50808,13 @@
         <v>1.37</v>
       </c>
       <c r="P201">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="Q201">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="R201">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S201">
         <v>2.76</v>
@@ -51265,13 +51265,13 @@
         <v>4.9</v>
       </c>
       <c r="G203">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H203">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="I203">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="J203">
         <v>4.7</v>
@@ -51301,7 +51301,7 @@
         <v>1.77</v>
       </c>
       <c r="S203">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="T203">
         <v>1.48</v>
@@ -51310,7 +51310,7 @@
         <v>2.38</v>
       </c>
       <c r="V203">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="W203">
         <v>1.2</v>
@@ -51510,7 +51510,7 @@
         <v>2.18</v>
       </c>
       <c r="H204">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I204">
         <v>4.2</v>
@@ -51519,7 +51519,7 @@
         <v>3.95</v>
       </c>
       <c r="K204">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L204">
         <v>1.01</v>
@@ -51994,7 +51994,7 @@
         <v>1.61</v>
       </c>
       <c r="H206">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I206">
         <v>6.8</v>
@@ -52003,7 +52003,7 @@
         <v>4.3</v>
       </c>
       <c r="K206">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L206">
         <v>1.01</v>
@@ -52012,16 +52012,16 @@
         <v>1.04</v>
       </c>
       <c r="N206">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O206">
         <v>1.22</v>
       </c>
       <c r="P206">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q206">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="R206">
         <v>1.45</v>
@@ -52033,7 +52033,7 @@
         <v>1.71</v>
       </c>
       <c r="U206">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V206">
         <v>1.17</v>
@@ -52293,7 +52293,7 @@
         <v>34</v>
       </c>
       <c r="AA207">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB207">
         <v>34</v>
@@ -52329,16 +52329,16 @@
         <v>1000</v>
       </c>
       <c r="AM207">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN207">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO207">
         <v>11</v>
       </c>
       <c r="AP207">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AQ207">
         <v>17.5</v>
@@ -52347,49 +52347,49 @@
         <v>18</v>
       </c>
       <c r="AS207">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AT207">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AU207">
-        <v>1.25</v>
+        <v>10.5</v>
       </c>
       <c r="AV207">
-        <v>1.25</v>
+        <v>11</v>
       </c>
       <c r="AW207">
-        <v>1.25</v>
+        <v>17</v>
       </c>
       <c r="AX207">
         <v>20</v>
       </c>
       <c r="AY207">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AZ207">
-        <v>1.25</v>
+        <v>11</v>
       </c>
       <c r="BA207">
-        <v>1.25</v>
+        <v>18</v>
       </c>
       <c r="BB207">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="BC207">
-        <v>1.25</v>
+        <v>19</v>
       </c>
       <c r="BD207">
-        <v>1.25</v>
+        <v>19</v>
       </c>
       <c r="BE207">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="BF207">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG207">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="BH207">
         <v>1000</v>
@@ -52502,16 +52502,16 @@
         <v>1.01</v>
       </c>
       <c r="P208">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q208">
         <v>1.02</v>
       </c>
       <c r="R208">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S208">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="T208">
         <v>1.01</v>
@@ -52956,7 +52956,7 @@
         <v>641</v>
       </c>
       <c r="F210">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G210">
         <v>1.67</v>
@@ -52980,16 +52980,16 @@
         <v>1.01</v>
       </c>
       <c r="N210">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="O210">
         <v>1.29</v>
       </c>
       <c r="P210">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q210">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R210">
         <v>1.3</v>
@@ -53213,7 +53213,7 @@
         <v>3.75</v>
       </c>
       <c r="K211">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L211">
         <v>1.01</v>
@@ -53228,10 +53228,10 @@
         <v>1.23</v>
       </c>
       <c r="P211">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="Q211">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R211">
         <v>1.35</v>
@@ -53443,7 +53443,7 @@
         <v>1.6</v>
       </c>
       <c r="G212">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H212">
         <v>4.6</v>
@@ -53491,7 +53491,7 @@
         <v>1.16</v>
       </c>
       <c r="W212">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X212">
         <v>1000</v>
@@ -53706,16 +53706,16 @@
         <v>1.05</v>
       </c>
       <c r="N213">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O213">
         <v>1.23</v>
       </c>
       <c r="P213">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q213">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R213">
         <v>1.48</v>
@@ -54453,7 +54453,7 @@
         <v>1.01</v>
       </c>
       <c r="U216">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V216">
         <v>1.63</v>
@@ -54806,7 +54806,7 @@
         <v>42</v>
       </c>
       <c r="BF217">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG217">
         <v>70</v>
@@ -54916,22 +54916,22 @@
         <v>1.09</v>
       </c>
       <c r="N218">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O218">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P218">
         <v>1.79</v>
       </c>
       <c r="Q218">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R218">
         <v>1.29</v>
       </c>
       <c r="S218">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T218">
         <v>1.89</v>
@@ -54952,7 +54952,7 @@
         <v>10.5</v>
       </c>
       <c r="Z218">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA218">
         <v>50</v>
@@ -54997,7 +54997,7 @@
         <v>32</v>
       </c>
       <c r="AO218">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP218">
         <v>10.5</v>
@@ -55158,7 +55158,7 @@
         <v>1.06</v>
       </c>
       <c r="N219">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O219">
         <v>1.3</v>
@@ -55167,7 +55167,7 @@
         <v>2.04</v>
       </c>
       <c r="Q219">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R219">
         <v>1.4</v>
@@ -55176,7 +55176,7 @@
         <v>3.25</v>
       </c>
       <c r="T219">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U219">
         <v>2.14</v>
@@ -55406,7 +55406,7 @@
         <v>1.27</v>
       </c>
       <c r="P220">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q220">
         <v>1.71</v>
@@ -55424,7 +55424,7 @@
         <v>1.99</v>
       </c>
       <c r="V220">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W220">
         <v>1.72</v>
@@ -55618,7 +55618,7 @@
         <v>652</v>
       </c>
       <c r="F221">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="G221">
         <v>1.74</v>
@@ -55884,7 +55884,7 @@
         <v>1.01</v>
       </c>
       <c r="N222">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O222">
         <v>1.02</v>
@@ -56102,7 +56102,7 @@
         <v>654</v>
       </c>
       <c r="F223">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G223">
         <v>4.2</v>
@@ -56135,7 +56135,7 @@
         <v>1.85</v>
       </c>
       <c r="Q223">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="R223">
         <v>1.25</v>
@@ -56344,7 +56344,7 @@
         <v>655</v>
       </c>
       <c r="F224">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G224">
         <v>1.55</v>
@@ -56359,7 +56359,7 @@
         <v>4.7</v>
       </c>
       <c r="K224">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L224">
         <v>1.36</v>
@@ -56458,7 +56458,7 @@
         <v>22</v>
       </c>
       <c r="AR224">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AS224">
         <v>46</v>
@@ -56473,7 +56473,7 @@
         <v>23</v>
       </c>
       <c r="AW224">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AX224">
         <v>8.6</v>
@@ -56485,7 +56485,7 @@
         <v>20</v>
       </c>
       <c r="BA224">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB224">
         <v>12.5</v>
@@ -56494,7 +56494,7 @@
         <v>14</v>
       </c>
       <c r="BD224">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE224">
         <v>40</v>
@@ -56658,7 +56658,7 @@
         <v>12.5</v>
       </c>
       <c r="AD225">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE225">
         <v>14.5</v>
@@ -56730,16 +56730,16 @@
         <v>23</v>
       </c>
       <c r="BB225">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC225">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD225">
         <v>55</v>
       </c>
       <c r="BE225">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF225">
         <v>55</v>
@@ -56861,13 +56861,13 @@
         <v>2.4</v>
       </c>
       <c r="Q226">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="R226">
         <v>1.52</v>
       </c>
       <c r="S226">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="T226">
         <v>1.48</v>
@@ -57796,7 +57796,7 @@
         <v>661</v>
       </c>
       <c r="F230">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G230">
         <v>2.24</v>
@@ -57811,31 +57811,31 @@
         <v>3.55</v>
       </c>
       <c r="K230">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L230">
         <v>1.01</v>
       </c>
       <c r="M230">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N230">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O230">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P230">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q230">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R230">
         <v>1.31</v>
       </c>
       <c r="S230">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="T230">
         <v>1.01</v>
@@ -57844,7 +57844,7 @@
         <v>2.12</v>
       </c>
       <c r="V230">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W230">
         <v>1.8</v>
@@ -57931,7 +57931,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY230">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ230">
         <v>2.44</v>
@@ -58068,7 +58068,7 @@
         <v>1.15</v>
       </c>
       <c r="P231">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q231">
         <v>1.15</v>
@@ -58077,7 +58077,7 @@
         <v>1.18</v>
       </c>
       <c r="S231">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T231">
         <v>1.03</v>
@@ -58101,7 +58101,7 @@
         <v>95</v>
       </c>
       <c r="AA231">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="AB231">
         <v>48</v>
@@ -58110,55 +58110,55 @@
         <v>26</v>
       </c>
       <c r="AD231">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE231">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="AF231">
         <v>32</v>
       </c>
       <c r="AG231">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH231">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AI231">
-        <v>650</v>
+        <v>480</v>
       </c>
       <c r="AJ231">
         <v>32</v>
       </c>
       <c r="AK231">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL231">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AM231">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AN231">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO231">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP231">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ231">
         <v>10.5</v>
       </c>
       <c r="AR231">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AS231">
         <v>110</v>
       </c>
       <c r="AT231">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU231">
         <v>7.2</v>
@@ -58283,7 +58283,7 @@
         <v>3.75</v>
       </c>
       <c r="G232">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H232">
         <v>1.85</v>
@@ -58304,19 +58304,19 @@
         <v>1.01</v>
       </c>
       <c r="N232">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="O232">
         <v>1.38</v>
       </c>
       <c r="P232">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="Q232">
         <v>1.96</v>
       </c>
       <c r="R232">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S232">
         <v>3.35</v>
@@ -58331,7 +58331,7 @@
         <v>1.81</v>
       </c>
       <c r="W232">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X232">
         <v>1000</v>
@@ -58388,52 +58388,52 @@
         <v>1000</v>
       </c>
       <c r="AP232">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ232">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR232">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS232">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AT232">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU232">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV232">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW232">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX232">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY232">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ232">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA232">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB232">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC232">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD232">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE232">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF232">
         <v>1.01</v>
@@ -58525,19 +58525,19 @@
         <v>3.45</v>
       </c>
       <c r="G233">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H233">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I233">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J233">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K233">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -58797,19 +58797,19 @@
         <v>3.15</v>
       </c>
       <c r="Q234">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R234">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S234">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="T234">
         <v>2.06</v>
       </c>
       <c r="U234">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V234">
         <v>1.05</v>
@@ -58818,112 +58818,112 @@
         <v>5.3</v>
       </c>
       <c r="X234">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y234">
         <v>70</v>
       </c>
       <c r="Z234">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA234">
         <v>1000</v>
       </c>
       <c r="AB234">
+        <v>12.5</v>
+      </c>
+      <c r="AC234">
+        <v>18.5</v>
+      </c>
+      <c r="AD234">
+        <v>65</v>
+      </c>
+      <c r="AE234">
+        <v>330</v>
+      </c>
+      <c r="AF234">
+        <v>9.4</v>
+      </c>
+      <c r="AG234">
+        <v>12.5</v>
+      </c>
+      <c r="AH234">
+        <v>38</v>
+      </c>
+      <c r="AI234">
+        <v>220</v>
+      </c>
+      <c r="AJ234">
+        <v>9.4</v>
+      </c>
+      <c r="AK234">
         <v>14.5</v>
       </c>
-      <c r="AC234">
-        <v>21</v>
-      </c>
-      <c r="AD234">
-        <v>70</v>
-      </c>
-      <c r="AE234">
-        <v>1000</v>
-      </c>
-      <c r="AF234">
-        <v>18.5</v>
-      </c>
-      <c r="AG234">
+      <c r="AL234">
+        <v>42</v>
+      </c>
+      <c r="AM234">
+        <v>200</v>
+      </c>
+      <c r="AN234">
+        <v>3.4</v>
+      </c>
+      <c r="AO234">
+        <v>390</v>
+      </c>
+      <c r="AP234">
+        <v>9</v>
+      </c>
+      <c r="AQ234">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR234">
+        <v>11</v>
+      </c>
+      <c r="AS234">
+        <v>11.5</v>
+      </c>
+      <c r="AT234">
+        <v>10</v>
+      </c>
+      <c r="AU234">
         <v>15</v>
       </c>
-      <c r="AH234">
-        <v>42</v>
-      </c>
-      <c r="AI234">
-        <v>1000</v>
-      </c>
-      <c r="AJ234">
-        <v>13.5</v>
-      </c>
-      <c r="AK234">
-        <v>16.5</v>
-      </c>
-      <c r="AL234">
-        <v>46</v>
-      </c>
-      <c r="AM234">
-        <v>1000</v>
-      </c>
-      <c r="AN234">
-        <v>3.7</v>
-      </c>
-      <c r="AO234">
-        <v>1000</v>
-      </c>
-      <c r="AP234">
-        <v>3.5</v>
-      </c>
-      <c r="AQ234">
-        <v>3.4</v>
-      </c>
-      <c r="AR234">
-        <v>3.5</v>
-      </c>
-      <c r="AS234">
-        <v>3.5</v>
-      </c>
-      <c r="AT234">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU234">
-        <v>14</v>
-      </c>
       <c r="AV234">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW234">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AX234">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY234">
+        <v>10.5</v>
+      </c>
+      <c r="AZ234">
         <v>9.4</v>
       </c>
-      <c r="AZ234">
-        <v>3.25</v>
-      </c>
       <c r="BA234">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BB234">
-        <v>2.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC234">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD234">
-        <v>23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE234">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="BF234">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BG234">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="BH234">
         <v>1000</v>
@@ -59009,19 +59009,19 @@
         <v>1.68</v>
       </c>
       <c r="G235">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H235">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="I235">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K235">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L235">
         <v>1.01</v>
@@ -59057,7 +59057,7 @@
         <v>1.24</v>
       </c>
       <c r="W235">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X235">
         <v>1000</v>
@@ -59272,22 +59272,22 @@
         <v>1.01</v>
       </c>
       <c r="N236">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O236">
         <v>1.02</v>
       </c>
       <c r="P236">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q236">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="R236">
         <v>1.12</v>
       </c>
       <c r="S236">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="T236">
         <v>1.01</v>
@@ -59490,22 +59490,22 @@
         <v>668</v>
       </c>
       <c r="F237">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G237">
         <v>2.36</v>
       </c>
       <c r="H237">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="I237">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J237">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K237">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="L237">
         <v>1.01</v>
@@ -59514,7 +59514,7 @@
         <v>1.02</v>
       </c>
       <c r="N237">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O237">
         <v>1.29</v>
@@ -59526,7 +59526,7 @@
         <v>2.44</v>
       </c>
       <c r="R237">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="S237">
         <v>2.92</v>
@@ -59538,7 +59538,7 @@
         <v>1.01</v>
       </c>
       <c r="V237">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W237">
         <v>1.74</v>
